--- a/backups/warsgate_accounting_backup_latest.xlsx
+++ b/backups/warsgate_accounting_backup_latest.xlsx
@@ -704,7 +704,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -778,13 +778,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>prod-1</v>
+        <v>prod-box-minijb01</v>
       </c>
       <c r="B3" t="str">
-        <v>PLC-S7-1200</v>
+        <v>BOX-MINI-JB01</v>
       </c>
       <c r="C3" t="str">
-        <v>Siemens PLC SIMATIC S7-1200 CPU 1214C DC/DC/DC</v>
+        <v>mini junction box</v>
       </c>
       <c r="D3" t="str">
         <v>PRODUCT</v>
@@ -793,33 +793,33 @@
         <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F3" t="str">
-        <v>เครื่อง</v>
+        <v>Set</v>
       </c>
       <c r="G3">
-        <v>18500</v>
+        <v>300</v>
       </c>
       <c r="H3">
-        <v>13200</v>
+        <v>300</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3" t="str">
-        <v>โปรแกรมเมเบิลคอนโทรลเลอร์ 14 DI / 10 DO / 2 AI</v>
+        <v>mini junction box</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>prod-2</v>
+        <v>prod-1</v>
       </c>
       <c r="B4" t="str">
-        <v>SERVO-750W</v>
+        <v>PLC-S7-1200</v>
       </c>
       <c r="C4" t="str">
-        <v>Omron Servo Motor &amp; Driver Set 750W 3000RPM</v>
+        <v>Siemens PLC SIMATIC S7-1200 CPU 1214C DC/DC/DC</v>
       </c>
       <c r="D4" t="str">
         <v>PRODUCT</v>
@@ -828,33 +828,33 @@
         <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F4" t="str">
-        <v>ชุด</v>
+        <v>เครื่อง</v>
       </c>
       <c r="G4">
-        <v>24500</v>
+        <v>18500</v>
       </c>
       <c r="H4">
-        <v>17800</v>
+        <v>13200</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4" t="str">
-        <v>ชุดเซอร์โวมอเตอร์และไดรเวอร์ความแม่นยำสูง</v>
+        <v>โปรแกรมเมเบิลคอนโทรลเลอร์ 14 DI / 10 DO / 2 AI</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>prod-3</v>
+        <v>prod-2</v>
       </c>
       <c r="B5" t="str">
-        <v>HMI-KTP700</v>
+        <v>SERVO-750W</v>
       </c>
       <c r="C5" t="str">
-        <v>Siemens Touch Panel HMI KTP700 Basic 7 นิ้ว</v>
+        <v>Omron Servo Motor &amp; Driver Set 750W 3000RPM</v>
       </c>
       <c r="D5" t="str">
         <v>PRODUCT</v>
@@ -863,68 +863,68 @@
         <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F5" t="str">
-        <v>เครื่อง</v>
+        <v>ชุด</v>
       </c>
       <c r="G5">
-        <v>16800</v>
+        <v>24500</v>
       </c>
       <c r="H5">
-        <v>12100</v>
+        <v>17800</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="str">
-        <v>หน้าจอสัมผัสควบคุมเครื่องจักรความละเอียดสูง</v>
+        <v>ชุดเซอร์โวมอเตอร์และไดรเวอร์ความแม่นยำสูง</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>prod-4</v>
+        <v>prod-3</v>
       </c>
       <c r="B6" t="str">
-        <v>ENG-PROGRAMMING</v>
+        <v>HMI-KTP700</v>
       </c>
       <c r="C6" t="str">
-        <v>ค่าบริการเขียนโปรแกรม PLC / SCADA &amp; HMI Design</v>
+        <v>Siemens Touch Panel HMI KTP700 Basic 7 นิ้ว</v>
       </c>
       <c r="D6" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E6" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F6" t="str">
-        <v>Man-Day</v>
+        <v>เครื่อง</v>
       </c>
       <c r="G6">
-        <v>15000</v>
+        <v>16800</v>
       </c>
       <c r="H6">
-        <v>7500</v>
+        <v>12100</v>
       </c>
       <c r="I6">
-        <v>999</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K6" t="str">
-        <v>วิศวกรผู้เชี่ยวชาญออกแบบและพัฒนาโปรแกรมควบคุมไลน์ผลิต</v>
+        <v>หน้าจอสัมผัสควบคุมเครื่องจักรความละเอียดสูง</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>prod-5</v>
+        <v>prod-4</v>
       </c>
       <c r="B7" t="str">
-        <v>ENG-COMMISSION</v>
+        <v>ENG-PROGRAMMING</v>
       </c>
       <c r="C7" t="str">
-        <v>ค่าบริการทดสอบและติดตั้งระบบหน้างาน (On-site Commissioning)</v>
+        <v>ค่าบริการเขียนโปรแกรม PLC / SCADA &amp; HMI Design</v>
       </c>
       <c r="D7" t="str">
         <v>SERVICE</v>
@@ -936,10 +936,10 @@
         <v>Man-Day</v>
       </c>
       <c r="G7">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="H7">
-        <v>6000</v>
+        <v>7500</v>
       </c>
       <c r="I7">
         <v>999</v>
@@ -948,33 +948,33 @@
         <v>0</v>
       </c>
       <c r="K7" t="str">
-        <v>ทดสอบความปลอดภัยและการทำงานของไลน์การผลิตหน้าโรงงาน</v>
+        <v>วิศวกรผู้เชี่ยวชาญออกแบบและพัฒนาโปรแกรมควบคุมไลน์ผลิต</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>prod-trace-1</v>
+        <v>prod-5</v>
       </c>
       <c r="B8" t="str">
-        <v>SW-TRACE-001</v>
+        <v>ENG-COMMISSION</v>
       </c>
       <c r="C8" t="str">
-        <v>Traceability Solenoid Line Software</v>
+        <v>ค่าบริการทดสอบและติดตั้งระบบหน้างาน (On-site Commissioning)</v>
       </c>
       <c r="D8" t="str">
         <v>SERVICE</v>
       </c>
       <c r="E8" t="str">
-        <v>SOFTWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F8" t="str">
-        <v>Job</v>
+        <v>Man-Day</v>
       </c>
       <c r="G8">
-        <v>2023419</v>
+        <v>12000</v>
       </c>
       <c r="H8">
-        <v>850000</v>
+        <v>6000</v>
       </c>
       <c r="I8">
         <v>999</v>
@@ -983,18 +983,18 @@
         <v>0</v>
       </c>
       <c r="K8" t="str">
-        <v>ซอฟต์แวร์ระบบตรวจสอบย้อนกลับ (Traceability) สายการผลิต Solenoid Line</v>
+        <v>ทดสอบความปลอดภัยและการทำงานของไลน์การผลิตหน้าโรงงาน</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>prod-trace-2</v>
+        <v>prod-trace-1</v>
       </c>
       <c r="B9" t="str">
-        <v>SW-TRACE-002</v>
+        <v>SW-TRACE-001</v>
       </c>
       <c r="C9" t="str">
-        <v>Traceability Solenoid Line Software เพิ่มเติม</v>
+        <v>Traceability Solenoid Line Software</v>
       </c>
       <c r="D9" t="str">
         <v>SERVICE</v>
@@ -1006,10 +1006,10 @@
         <v>Job</v>
       </c>
       <c r="G9">
-        <v>150000</v>
+        <v>2023419</v>
       </c>
       <c r="H9">
-        <v>60000</v>
+        <v>850000</v>
       </c>
       <c r="I9">
         <v>999</v>
@@ -1018,33 +1018,33 @@
         <v>0</v>
       </c>
       <c r="K9" t="str">
-        <v>ซอฟต์แวร์ฟังก์ชันเพิ่มเติม Traceability Solenoid Line</v>
+        <v>ซอฟต์แวร์ระบบตรวจสอบย้อนกลับ (Traceability) สายการผลิต Solenoid Line</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>prod-6</v>
+        <v>prod-trace-2</v>
       </c>
       <c r="B10" t="str">
-        <v>MAINT-ANNUAL</v>
+        <v>SW-TRACE-002</v>
       </c>
       <c r="C10" t="str">
-        <v>สัญญาบริการบำรุงรักษาระบบอัตโนมัติรายปี (Annual PM Contract)</v>
+        <v>Traceability Solenoid Line Software เพิ่มเติม</v>
       </c>
       <c r="D10" t="str">
         <v>SERVICE</v>
       </c>
       <c r="E10" t="str">
-        <v>MAINTENANCE</v>
+        <v>SOFTWARE</v>
       </c>
       <c r="F10" t="str">
-        <v>สัญญา</v>
+        <v>Job</v>
       </c>
       <c r="G10">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="H10">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="I10">
         <v>999</v>
@@ -1053,53 +1053,53 @@
         <v>0</v>
       </c>
       <c r="K10" t="str">
-        <v>เข้าตรวจเช็คระบบรายไตรมาส (4 ครั้ง/ปี) พร้อม On-call 24 ชม.</v>
+        <v>ซอฟต์แวร์ฟังก์ชันเพิ่มเติม Traceability Solenoid Line</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>prod-tsf-1</v>
+        <v>prod-6</v>
       </c>
       <c r="B11" t="str">
-        <v>TSF-ST-001</v>
+        <v>MAINT-ANNUAL</v>
       </c>
       <c r="C11" t="str">
-        <v>Station Stacker Foam</v>
+        <v>สัญญาบริการบำรุงรักษาระบบอัตโนมัติรายปี (Annual PM Contract)</v>
       </c>
       <c r="D11" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E11" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>MAINTENANCE</v>
       </c>
       <c r="F11" t="str">
-        <v>SET</v>
+        <v>สัญญา</v>
       </c>
       <c r="G11">
-        <v>765394</v>
+        <v>120000</v>
       </c>
       <c r="H11">
-        <v>420000</v>
+        <v>40000</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="str">
-        <v>ชุดสถานีเรียงโฟมอัตโนมัติ (Station Stacker Foam) เครื่อง TSF1 Auto pack LM1</v>
+        <v>เข้าตรวจเช็คระบบรายไตรมาส (4 ครั้ง/ปี) พร้อม On-call 24 ชม.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>prod-tsf-2</v>
+        <v>prod-tsf-1</v>
       </c>
       <c r="B12" t="str">
-        <v>TSF-ST-002</v>
+        <v>TSF-ST-001</v>
       </c>
       <c r="C12" t="str">
-        <v>Station Open Bag &amp; Insert Foam</v>
+        <v>Station Stacker Foam</v>
       </c>
       <c r="D12" t="str">
         <v>PRODUCT</v>
@@ -1111,10 +1111,10 @@
         <v>SET</v>
       </c>
       <c r="G12">
-        <v>650215</v>
+        <v>765394</v>
       </c>
       <c r="H12">
-        <v>350000</v>
+        <v>420000</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -1123,18 +1123,18 @@
         <v>0</v>
       </c>
       <c r="K12" t="str">
-        <v>ชุดสถานีเปิดถุงและบรรจุโฟม (Station Open Bag &amp; Insert Foam)</v>
+        <v>ชุดสถานีเรียงโฟมอัตโนมัติ (Station Stacker Foam) เครื่อง TSF1 Auto pack LM1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>prod-tsf-3</v>
+        <v>prod-tsf-2</v>
       </c>
       <c r="B13" t="str">
-        <v>TSF-ST-003</v>
+        <v>TSF-ST-002</v>
       </c>
       <c r="C13" t="str">
-        <v>Station Pallet Stacker Foam</v>
+        <v>Station Open Bag &amp; Insert Foam</v>
       </c>
       <c r="D13" t="str">
         <v>PRODUCT</v>
@@ -1146,10 +1146,10 @@
         <v>SET</v>
       </c>
       <c r="G13">
-        <v>690391</v>
+        <v>650215</v>
       </c>
       <c r="H13">
-        <v>380000</v>
+        <v>350000</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -1158,18 +1158,18 @@
         <v>0</v>
       </c>
       <c r="K13" t="str">
-        <v>ชุดสถานีเรียงพาเลทโฟม (Station Pallet Stacker Foam)</v>
+        <v>ชุดสถานีเปิดถุงและบรรจุโฟม (Station Open Bag &amp; Insert Foam)</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>prod-tsf-4</v>
+        <v>prod-tsf-3</v>
       </c>
       <c r="B14" t="str">
-        <v>TSF-ST-004</v>
+        <v>TSF-ST-003</v>
       </c>
       <c r="C14" t="str">
-        <v>Contron Box System</v>
+        <v>Station Pallet Stacker Foam</v>
       </c>
       <c r="D14" t="str">
         <v>PRODUCT</v>
@@ -1181,10 +1181,10 @@
         <v>SET</v>
       </c>
       <c r="G14">
-        <v>312000</v>
+        <v>690391</v>
       </c>
       <c r="H14">
-        <v>170000</v>
+        <v>380000</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -1193,33 +1193,33 @@
         <v>0</v>
       </c>
       <c r="K14" t="str">
-        <v>ตู้ควบคุมระบบไฟฟ้าและ PLC คอนโทรลเลอร์ (Control Box System)</v>
+        <v>ชุดสถานีเรียงพาเลทโฟม (Station Pallet Stacker Foam)</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>prod-tsf-5</v>
+        <v>prod-tsf-4</v>
       </c>
       <c r="B15" t="str">
-        <v>TSF-SRV-001</v>
+        <v>TSF-ST-004</v>
       </c>
       <c r="C15" t="str">
-        <v>Manpower and labor cost</v>
+        <v>Contron Box System</v>
       </c>
       <c r="D15" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E15" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F15" t="str">
-        <v>JOB</v>
+        <v>SET</v>
       </c>
       <c r="G15">
-        <v>575000</v>
+        <v>312000</v>
       </c>
       <c r="H15">
-        <v>280000</v>
+        <v>170000</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -1228,18 +1228,18 @@
         <v>0</v>
       </c>
       <c r="K15" t="str">
-        <v>ค่าแรงวิศวกร ประกอบ ติดตั้ง และทดสอบระบบ TSF1 Auto pack LM1</v>
+        <v>ตู้ควบคุมระบบไฟฟ้าและ PLC คอนโทรลเลอร์ (Control Box System)</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>prod-tsf-6</v>
+        <v>prod-tsf-5</v>
       </c>
       <c r="B16" t="str">
-        <v>TSF-SRV-002</v>
+        <v>TSF-SRV-001</v>
       </c>
       <c r="C16" t="str">
-        <v>Transportation and accommodation</v>
+        <v>Manpower and labor cost</v>
       </c>
       <c r="D16" t="str">
         <v>SERVICE</v>
@@ -1251,10 +1251,10 @@
         <v>JOB</v>
       </c>
       <c r="G16">
-        <v>45000</v>
+        <v>575000</v>
       </c>
       <c r="H16">
-        <v>30000</v>
+        <v>280000</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -1263,18 +1263,18 @@
         <v>0</v>
       </c>
       <c r="K16" t="str">
-        <v>ค่าขนส่งเครื่องจักรและค่าที่พักเดินทางหน้างานโรงงานชลบุรี</v>
+        <v>ค่าแรงวิศวกร ประกอบ ติดตั้ง และทดสอบระบบ TSF1 Auto pack LM1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>prod-tsf-7</v>
+        <v>prod-tsf-6</v>
       </c>
       <c r="B17" t="str">
-        <v>TSF-SRV-003</v>
+        <v>TSF-SRV-002</v>
       </c>
       <c r="C17" t="str">
-        <v>Profit / Project Management &amp; Warranty 1 year</v>
+        <v>Transportation and accommodation</v>
       </c>
       <c r="D17" t="str">
         <v>SERVICE</v>
@@ -1286,10 +1286,10 @@
         <v>JOB</v>
       </c>
       <c r="G17">
-        <v>607600</v>
+        <v>45000</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -1298,53 +1298,53 @@
         <v>0</v>
       </c>
       <c r="K17" t="str">
-        <v>ค่าบริหารโครงการ บริการหลังการขาย และรับประกันระบบ 1 ปี (Warranty 1 year)</v>
+        <v>ค่าขนส่งเครื่องจักรและค่าที่พักเดินทางหน้างานโรงงานชลบุรี</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>prod-pnp-corr</v>
+        <v>prod-tsf-7</v>
       </c>
       <c r="B18" t="str">
-        <v>SW-TRACE-CORR</v>
+        <v>TSF-SRV-003</v>
       </c>
       <c r="C18" t="str">
-        <v>Traceability Corrugating Line</v>
+        <v>Profit / Project Management &amp; Warranty 1 year</v>
       </c>
       <c r="D18" t="str">
         <v>SERVICE</v>
       </c>
       <c r="E18" t="str">
-        <v>SOFTWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F18" t="str">
-        <v>Job</v>
+        <v>JOB</v>
       </c>
       <c r="G18">
-        <v>1005002.64</v>
+        <v>607600</v>
       </c>
       <c r="H18">
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18" t="str">
-        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Corrugating Line โครงการ Fujipart (PO: 2505004)</v>
+        <v>ค่าบริหารโครงการ บริการหลังการขาย และรับประกันระบบ 1 ปี (Warranty 1 year)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>prod-pnp-wind</v>
+        <v>prod-pnp-corr</v>
       </c>
       <c r="B19" t="str">
-        <v>SW-TRACE-WIND</v>
+        <v>SW-TRACE-CORR</v>
       </c>
       <c r="C19" t="str">
-        <v>Traceability Winding Line</v>
+        <v>Traceability Corrugating Line</v>
       </c>
       <c r="D19" t="str">
         <v>SERVICE</v>
@@ -1356,10 +1356,10 @@
         <v>Job</v>
       </c>
       <c r="G19">
-        <v>707304.38</v>
+        <v>1005002.64</v>
       </c>
       <c r="H19">
-        <v>320000</v>
+        <v>450000</v>
       </c>
       <c r="I19">
         <v>999</v>
@@ -1368,18 +1368,18 @@
         <v>0</v>
       </c>
       <c r="K19" t="str">
-        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Winding Line โครงการ Fujipart (PO: 2505004)</v>
+        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Corrugating Line โครงการ Fujipart (PO: 2505004)</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>prod-pnp-adh</v>
+        <v>prod-pnp-wind</v>
       </c>
       <c r="B20" t="str">
-        <v>SW-TRACE-ADH</v>
+        <v>SW-TRACE-WIND</v>
       </c>
       <c r="C20" t="str">
-        <v>Traceability Adhesive &amp; Spin Winding Line</v>
+        <v>Traceability Winding Line</v>
       </c>
       <c r="D20" t="str">
         <v>SERVICE</v>
@@ -1391,10 +1391,10 @@
         <v>Job</v>
       </c>
       <c r="G20">
-        <v>874426.94</v>
+        <v>707304.38</v>
       </c>
       <c r="H20">
-        <v>390000</v>
+        <v>320000</v>
       </c>
       <c r="I20">
         <v>999</v>
@@ -1403,18 +1403,18 @@
         <v>0</v>
       </c>
       <c r="K20" t="str">
-        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Adhesive &amp; Spin Winding Line โครงการ Fujipart (PO: 2505004)</v>
+        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Winding Line โครงการ Fujipart (PO: 2505004)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>prod-pnp-df4</v>
+        <v>prod-pnp-adh</v>
       </c>
       <c r="B21" t="str">
-        <v>SW-TRACE-DF4</v>
+        <v>SW-TRACE-ADH</v>
       </c>
       <c r="C21" t="str">
-        <v>Traceability DF4 Line</v>
+        <v>Traceability Adhesive &amp; Spin Winding Line</v>
       </c>
       <c r="D21" t="str">
         <v>SERVICE</v>
@@ -1426,10 +1426,10 @@
         <v>Job</v>
       </c>
       <c r="G21">
-        <v>1203060.14</v>
+        <v>874426.94</v>
       </c>
       <c r="H21">
-        <v>540000</v>
+        <v>390000</v>
       </c>
       <c r="I21">
         <v>999</v>
@@ -1438,18 +1438,18 @@
         <v>0</v>
       </c>
       <c r="K21" t="str">
-        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต DF4 Line โครงการ Fujipart (PO: 2505004)</v>
+        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Adhesive &amp; Spin Winding Line โครงการ Fujipart (PO: 2505004)</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>prod-pnp-pack</v>
+        <v>prod-pnp-df4</v>
       </c>
       <c r="B22" t="str">
-        <v>SW-TRACE-PACK</v>
+        <v>SW-TRACE-DF4</v>
       </c>
       <c r="C22" t="str">
-        <v>Traceability Packing Line</v>
+        <v>Traceability DF4 Line</v>
       </c>
       <c r="D22" t="str">
         <v>SERVICE</v>
@@ -1461,10 +1461,10 @@
         <v>Job</v>
       </c>
       <c r="G22">
-        <v>553196.28</v>
+        <v>1203060.14</v>
       </c>
       <c r="H22">
-        <v>250000</v>
+        <v>540000</v>
       </c>
       <c r="I22">
         <v>999</v>
@@ -1473,68 +1473,68 @@
         <v>0</v>
       </c>
       <c r="K22" t="str">
-        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Packing Line โครงการ Fujipart (PO: 2505004)</v>
+        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต DF4 Line โครงการ Fujipart (PO: 2505004)</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>prod-pnp-fab</v>
+        <v>prod-pnp-pack</v>
       </c>
       <c r="B23" t="str">
-        <v>PNP-FAB-001</v>
+        <v>SW-TRACE-PACK</v>
       </c>
       <c r="C23" t="str">
-        <v>Standard and Feb Part (Zone 1-6)</v>
+        <v>Traceability Packing Line</v>
       </c>
       <c r="D23" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E23" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>SOFTWARE</v>
       </c>
       <c r="F23" t="str">
-        <v>Set</v>
+        <v>Job</v>
       </c>
       <c r="G23">
-        <v>1140000</v>
+        <v>553196.28</v>
       </c>
       <c r="H23">
-        <v>650000</v>
+        <v>250000</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23" t="str">
-        <v>ชุดโครงสร้างมาตรฐานและชิ้นงานประกอบ Fabricated Parts Zone 1-6 (PO: 2605001)</v>
+        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Packing Line โครงการ Fujipart (PO: 2505004)</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>prod-pnp-labor-z</v>
+        <v>prod-pnp-fab</v>
       </c>
       <c r="B24" t="str">
-        <v>PNP-LAB-001</v>
+        <v>PNP-FAB-001</v>
       </c>
       <c r="C24" t="str">
-        <v>Manpower and Labor Cost (Zone 1-6)</v>
+        <v>Standard and Feb Part (Zone 1-6)</v>
       </c>
       <c r="D24" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E24" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F24" t="str">
-        <v>Job</v>
+        <v>Set</v>
       </c>
       <c r="G24">
-        <v>670000</v>
+        <v>1140000</v>
       </c>
       <c r="H24">
-        <v>350000</v>
+        <v>650000</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -1543,18 +1543,18 @@
         <v>0</v>
       </c>
       <c r="K24" t="str">
-        <v>ค่าแรงวิศวกรและทีมช่างประกอบ ติดตั้ง ทดสอบ Zone 1-6 (PO: 2605001)</v>
+        <v>ชุดโครงสร้างมาตรฐานและชิ้นงานประกอบ Fabricated Parts Zone 1-6 (PO: 2605001)</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>prod-pnp-trans-z</v>
+        <v>prod-pnp-labor-z</v>
       </c>
       <c r="B25" t="str">
-        <v>PNP-LOG-001</v>
+        <v>PNP-LAB-001</v>
       </c>
       <c r="C25" t="str">
-        <v>Transportation and accommodation (Zone 1-6)</v>
+        <v>Manpower and Labor Cost (Zone 1-6)</v>
       </c>
       <c r="D25" t="str">
         <v>SERVICE</v>
@@ -1563,13 +1563,13 @@
         <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F25" t="str">
-        <v>EA</v>
+        <v>Job</v>
       </c>
       <c r="G25">
-        <v>45000</v>
+        <v>670000</v>
       </c>
       <c r="H25">
-        <v>30000</v>
+        <v>350000</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -1578,18 +1578,18 @@
         <v>0</v>
       </c>
       <c r="K25" t="str">
-        <v>ค่าขนส่งและที่พักเดินทางหน้างาน Zone 1-6 (PO: 2605001)</v>
+        <v>ค่าแรงวิศวกรและทีมช่างประกอบ ติดตั้ง ทดสอบ Zone 1-6 (PO: 2605001)</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>prod-pnp-pm-z</v>
+        <v>prod-pnp-trans-z</v>
       </c>
       <c r="B26" t="str">
-        <v>PNP-PM-001</v>
+        <v>PNP-LOG-001</v>
       </c>
       <c r="C26" t="str">
-        <v>Project Management (Zone 1-6)</v>
+        <v>Transportation and accommodation (Zone 1-6)</v>
       </c>
       <c r="D26" t="str">
         <v>SERVICE</v>
@@ -1601,10 +1601,10 @@
         <v>EA</v>
       </c>
       <c r="G26">
-        <v>556500</v>
+        <v>45000</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="I26">
         <v>1</v>
@@ -1613,33 +1613,33 @@
         <v>0</v>
       </c>
       <c r="K26" t="str">
-        <v>ค่าบริหารจัดการโครงการ ควบคุมงาน และทดสอบระบบ Zone 1-6 (PO: 2605001)</v>
+        <v>ค่าขนส่งและที่พักเดินทางหน้างาน Zone 1-6 (PO: 2605001)</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>prod-pnp-fab-z7</v>
+        <v>prod-pnp-pm-z</v>
       </c>
       <c r="B27" t="str">
-        <v>PNP-FAB-002</v>
+        <v>PNP-PM-001</v>
       </c>
       <c r="C27" t="str">
-        <v>Standard and Feb Part (Zone 7)</v>
+        <v>Project Management (Zone 1-6)</v>
       </c>
       <c r="D27" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E27" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F27" t="str">
-        <v>Set</v>
+        <v>EA</v>
       </c>
       <c r="G27">
-        <v>641000</v>
+        <v>556500</v>
       </c>
       <c r="H27">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>1</v>
@@ -1648,33 +1648,33 @@
         <v>0</v>
       </c>
       <c r="K27" t="str">
-        <v>ชุดโครงสร้างมาตรฐานและชิ้นงานประกอบ Fabricated Parts Zone 7 (PO: 2605002)</v>
+        <v>ค่าบริหารจัดการโครงการ ควบคุมงาน และทดสอบระบบ Zone 1-6 (PO: 2605001)</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>prod-pnp-labor-z7</v>
+        <v>prod-pnp-fab-z7</v>
       </c>
       <c r="B28" t="str">
-        <v>PNP-LAB-002</v>
+        <v>PNP-FAB-002</v>
       </c>
       <c r="C28" t="str">
-        <v>Manpower and Labor Cost (Zone 7)</v>
+        <v>Standard and Feb Part (Zone 7)</v>
       </c>
       <c r="D28" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E28" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F28" t="str">
-        <v>Job</v>
+        <v>Set</v>
       </c>
       <c r="G28">
-        <v>220000</v>
+        <v>641000</v>
       </c>
       <c r="H28">
-        <v>110000</v>
+        <v>350000</v>
       </c>
       <c r="I28">
         <v>1</v>
@@ -1683,18 +1683,18 @@
         <v>0</v>
       </c>
       <c r="K28" t="str">
-        <v>ค่าแรงวิศวกรและทีมช่างประกอบ ติดตั้ง ทดสอบ Zone 7 (PO: 2605002)</v>
+        <v>ชุดโครงสร้างมาตรฐานและชิ้นงานประกอบ Fabricated Parts Zone 7 (PO: 2605002)</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>prod-pnp-trans-z7</v>
+        <v>prod-pnp-labor-z7</v>
       </c>
       <c r="B29" t="str">
-        <v>PNP-LOG-002</v>
+        <v>PNP-LAB-002</v>
       </c>
       <c r="C29" t="str">
-        <v>Transportation and accommodation (Zone 7)</v>
+        <v>Manpower and Labor Cost (Zone 7)</v>
       </c>
       <c r="D29" t="str">
         <v>SERVICE</v>
@@ -1703,13 +1703,13 @@
         <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F29" t="str">
-        <v>EA</v>
+        <v>Job</v>
       </c>
       <c r="G29">
-        <v>45000</v>
+        <v>220000</v>
       </c>
       <c r="H29">
-        <v>30000</v>
+        <v>110000</v>
       </c>
       <c r="I29">
         <v>1</v>
@@ -1718,18 +1718,18 @@
         <v>0</v>
       </c>
       <c r="K29" t="str">
-        <v>ค่าขนส่งและที่พักเดินทางหน้างาน Zone 7 (PO: 2605002)</v>
+        <v>ค่าแรงวิศวกรและทีมช่างประกอบ ติดตั้ง ทดสอบ Zone 7 (PO: 2605002)</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>prod-pnp-pm-z7</v>
+        <v>prod-pnp-trans-z7</v>
       </c>
       <c r="B30" t="str">
-        <v>PNP-PM-002</v>
+        <v>PNP-LOG-002</v>
       </c>
       <c r="C30" t="str">
-        <v>Project Management (Zone 7)</v>
+        <v>Transportation and accommodation (Zone 7)</v>
       </c>
       <c r="D30" t="str">
         <v>SERVICE</v>
@@ -1741,10 +1741,10 @@
         <v>EA</v>
       </c>
       <c r="G30">
-        <v>271800</v>
+        <v>45000</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="I30">
         <v>1</v>
@@ -1753,53 +1753,53 @@
         <v>0</v>
       </c>
       <c r="K30" t="str">
-        <v>ค่าบริหารจัดการโครงการ ควบคุมงาน และทดสอบระบบ Zone 7 (PO: 2605002)</v>
+        <v>ค่าขนส่งและที่พักเดินทางหน้างาน Zone 7 (PO: 2605002)</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>prod-pnp-plc-eth</v>
+        <v>prod-pnp-pm-z7</v>
       </c>
       <c r="B31" t="str">
-        <v>PLC-ETH-001</v>
+        <v>PNP-PM-002</v>
       </c>
       <c r="C31" t="str">
-        <v>PLC Control Board (Ethernet IP)</v>
+        <v>Project Management (Zone 7)</v>
       </c>
       <c r="D31" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E31" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F31" t="str">
         <v>EA</v>
       </c>
       <c r="G31">
-        <v>35040</v>
+        <v>271800</v>
       </c>
       <c r="H31">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="str">
-        <v>บอร์ดควบคุม PLC รองรับการเชื่อมต่อเครือข่าย Ethernet IP (PO: 2607001)</v>
+        <v>ค่าบริหารจัดการโครงการ ควบคุมงาน และทดสอบระบบ Zone 7 (PO: 2605002)</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>prod-pnp-sub-plc</v>
+        <v>prod-pnp-plc-eth</v>
       </c>
       <c r="B32" t="str">
-        <v>PLC-SUB-001</v>
+        <v>PLC-ETH-001</v>
       </c>
       <c r="C32" t="str">
-        <v>Sub PLC Box + Aceessories</v>
+        <v>PLC Control Board (Ethernet IP)</v>
       </c>
       <c r="D32" t="str">
         <v>PRODUCT</v>
@@ -1811,30 +1811,30 @@
         <v>EA</v>
       </c>
       <c r="G32">
-        <v>26000</v>
+        <v>35040</v>
       </c>
       <c r="H32">
-        <v>15000</v>
+        <v>22000</v>
       </c>
       <c r="I32">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32" t="str">
-        <v>ตู้ Sub PLC พร้อมอุปกรณ์ส่วนควบ Accessories (PO: 2607001)</v>
+        <v>บอร์ดควบคุม PLC รองรับการเชื่อมต่อเครือข่าย Ethernet IP (PO: 2607001)</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>prod-pnp-rack-pc</v>
+        <v>prod-pnp-sub-plc</v>
       </c>
       <c r="B33" t="str">
-        <v>PC-RACK-001</v>
+        <v>PLC-SUB-001</v>
       </c>
       <c r="C33" t="str">
-        <v>Rack PC Center</v>
+        <v>Sub PLC Box + Aceessories</v>
       </c>
       <c r="D33" t="str">
         <v>PRODUCT</v>
@@ -1846,45 +1846,45 @@
         <v>EA</v>
       </c>
       <c r="G33">
-        <v>12000</v>
+        <v>26000</v>
       </c>
       <c r="H33">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33" t="str">
-        <v>ตู้แร็คศูนย์คอมพิวเตอร์และเซิร์ฟเวอร์ Rack PC Center (PO: 2607001)</v>
+        <v>ตู้ Sub PLC พร้อมอุปกรณ์ส่วนควบ Accessories (PO: 2607001)</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>prod-pnp-plc-dc</v>
+        <v>prod-pnp-rack-pc</v>
       </c>
       <c r="B34" t="str">
-        <v>PLC-DC-001</v>
+        <v>PC-RACK-001</v>
       </c>
       <c r="C34" t="str">
-        <v>PLC Data Center Line</v>
+        <v>Rack PC Center</v>
       </c>
       <c r="D34" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E34" t="str">
-        <v>SOFTWARE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F34" t="str">
         <v>EA</v>
       </c>
       <c r="G34">
-        <v>150000</v>
+        <v>12000</v>
       </c>
       <c r="H34">
-        <v>80000</v>
+        <v>7000</v>
       </c>
       <c r="I34">
         <v>1</v>
@@ -1893,33 +1893,33 @@
         <v>0</v>
       </c>
       <c r="K34" t="str">
-        <v>ระบบศูนย์รวมและประมวลผลข้อมูลสายการผลิต PLC Data Center Line (PO: 2607001)</v>
+        <v>ตู้แร็คศูนย์คอมพิวเตอร์และเซิร์ฟเวอร์ Rack PC Center (PO: 2607001)</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>prod-pnp-struct-sup</v>
+        <v>prod-pnp-plc-dc</v>
       </c>
       <c r="B35" t="str">
-        <v>STR-SUP-001</v>
+        <v>PLC-DC-001</v>
       </c>
       <c r="C35" t="str">
-        <v>Stucture Support</v>
+        <v>PLC Data Center Line</v>
       </c>
       <c r="D35" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E35" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>SOFTWARE</v>
       </c>
       <c r="F35" t="str">
         <v>EA</v>
       </c>
       <c r="G35">
-        <v>20000</v>
+        <v>150000</v>
       </c>
       <c r="H35">
-        <v>10000</v>
+        <v>80000</v>
       </c>
       <c r="I35">
         <v>1</v>
@@ -1928,18 +1928,18 @@
         <v>0</v>
       </c>
       <c r="K35" t="str">
-        <v>ชุดโครงสร้างรองรับและฐานยึดอุปกรณ์ Structure Support (PO: 2607001)</v>
+        <v>ระบบศูนย์รวมและประมวลผลข้อมูลสายการผลิต PLC Data Center Line (PO: 2607001)</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>prod-pnp-pc-center</v>
+        <v>prod-pnp-struct-sup</v>
       </c>
       <c r="B36" t="str">
-        <v>PC-CTR-001</v>
+        <v>STR-SUP-001</v>
       </c>
       <c r="C36" t="str">
-        <v>PC Center</v>
+        <v>Stucture Support</v>
       </c>
       <c r="D36" t="str">
         <v>PRODUCT</v>
@@ -1951,10 +1951,10 @@
         <v>EA</v>
       </c>
       <c r="G36">
-        <v>123000</v>
+        <v>20000</v>
       </c>
       <c r="H36">
-        <v>75000</v>
+        <v>10000</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -1963,47 +1963,82 @@
         <v>0</v>
       </c>
       <c r="K36" t="str">
-        <v>เครื่องคอมพิวเตอร์แม่ข่ายประมวลผล PC Center (PO: 2607001)</v>
+        <v>ชุดโครงสร้างรองรับและฐานยึดอุปกรณ์ Structure Support (PO: 2607001)</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>prod-pnp-pm-2607</v>
+        <v>prod-pnp-pc-center</v>
       </c>
       <c r="B37" t="str">
-        <v>PNP-PM-2607</v>
+        <v>PC-CTR-001</v>
       </c>
       <c r="C37" t="str">
-        <v>Project Management (PO: 2607001)</v>
+        <v>PC Center</v>
       </c>
       <c r="D37" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E37" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F37" t="str">
         <v>EA</v>
       </c>
       <c r="G37">
+        <v>123000</v>
+      </c>
+      <c r="H37">
+        <v>75000</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" t="str">
+        <v>เครื่องคอมพิวเตอร์แม่ข่ายประมวลผล PC Center (PO: 2607001)</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>prod-pnp-pm-2607</v>
+      </c>
+      <c r="B38" t="str">
+        <v>PNP-PM-2607</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Project Management (PO: 2607001)</v>
+      </c>
+      <c r="D38" t="str">
+        <v>SERVICE</v>
+      </c>
+      <c r="E38" t="str">
+        <v>ENGINEERING_SERVICE</v>
+      </c>
+      <c r="F38" t="str">
+        <v>EA</v>
+      </c>
+      <c r="G38">
         <v>573552</v>
       </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37" t="str">
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" t="str">
         <v>ค่าบริหารจัดการโครงการ ควบคุมงาน และทดสอบระบบ (PO: 2607001)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K38"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3104,19 +3139,19 @@
         <v>2026-10-24</v>
       </c>
       <c r="I27">
-        <v>16500</v>
+        <v>21000</v>
       </c>
       <c r="J27">
-        <v>1155</v>
+        <v>1470</v>
       </c>
       <c r="K27">
-        <v>17655</v>
+        <v>22470</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>17655</v>
+        <v>22470</v>
       </c>
       <c r="N27" t="str">
         <v>APPROVED</v>
@@ -3137,7 +3172,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5794,9 +5829,38 @@
         <v>0</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>PO-2609-001</v>
+      </c>
+      <c r="B94" t="str">
+        <v>PURCHASE_ORDER</v>
+      </c>
+      <c r="C94" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="E94">
+        <v>2</v>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v>mini junction box</v>
+      </c>
+      <c r="H94">
+        <v>15</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Set</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L93"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L94"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/backups/warsgate_accounting_backup_latest.xlsx
+++ b/backups/warsgate_accounting_backup_latest.xlsx
@@ -761,10 +761,10 @@
         <v>Set</v>
       </c>
       <c r="G2">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="H2">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="I2">
         <v>15</v>
@@ -3139,19 +3139,19 @@
         <v>2026-10-24</v>
       </c>
       <c r="I27">
-        <v>21000</v>
+        <v>9000</v>
       </c>
       <c r="J27">
-        <v>1470</v>
+        <v>630</v>
       </c>
       <c r="K27">
-        <v>22470</v>
+        <v>9630</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>22470</v>
+        <v>9630</v>
       </c>
       <c r="N27" t="str">
         <v>APPROVED</v>

--- a/backups/warsgate_accounting_backup_latest.xlsx
+++ b/backups/warsgate_accounting_backup_latest.xlsx
@@ -704,7 +704,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -813,13 +813,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>prod-1</v>
+        <v>prod-or-pcb-01</v>
       </c>
       <c r="B4" t="str">
-        <v>PLC-S7-1200</v>
+        <v>OR-PCB-01</v>
       </c>
       <c r="C4" t="str">
-        <v>Siemens PLC SIMATIC S7-1200 CPU 1214C DC/DC/DC</v>
+        <v>PC Board</v>
       </c>
       <c r="D4" t="str">
         <v>PRODUCT</v>
@@ -828,33 +828,33 @@
         <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F4" t="str">
-        <v>เครื่อง</v>
+        <v>EA</v>
       </c>
       <c r="G4">
-        <v>18500</v>
+        <v>13000</v>
       </c>
       <c r="H4">
-        <v>13200</v>
+        <v>9500</v>
       </c>
       <c r="I4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K4" t="str">
-        <v>โปรแกรมเมเบิลคอนโทรลเลอร์ 14 DI / 10 DO / 2 AI</v>
+        <v>PC Board สำหรับ New Box OR</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>prod-2</v>
+        <v>prod-or-dio-01</v>
       </c>
       <c r="B5" t="str">
-        <v>SERVO-750W</v>
+        <v>OR-DIO-01</v>
       </c>
       <c r="C5" t="str">
-        <v>Omron Servo Motor &amp; Driver Set 750W 3000RPM</v>
+        <v>Board Digital Input / Output</v>
       </c>
       <c r="D5" t="str">
         <v>PRODUCT</v>
@@ -863,33 +863,33 @@
         <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F5" t="str">
-        <v>ชุด</v>
+        <v>EA</v>
       </c>
       <c r="G5">
-        <v>24500</v>
+        <v>6000</v>
       </c>
       <c r="H5">
-        <v>17800</v>
+        <v>4200</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" t="str">
-        <v>ชุดเซอร์โวมอเตอร์และไดรเวอร์ความแม่นยำสูง</v>
+        <v>Board Digital Input / Output สำหรับ New Box OR</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>prod-3</v>
+        <v>prod-or-psu-01</v>
       </c>
       <c r="B6" t="str">
-        <v>HMI-KTP700</v>
+        <v>OR-PSU-01</v>
       </c>
       <c r="C6" t="str">
-        <v>Siemens Touch Panel HMI KTP700 Basic 7 นิ้ว</v>
+        <v>AC To DC Power</v>
       </c>
       <c r="D6" t="str">
         <v>PRODUCT</v>
@@ -898,208 +898,208 @@
         <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F6" t="str">
-        <v>เครื่อง</v>
+        <v>EA</v>
       </c>
       <c r="G6">
-        <v>16800</v>
+        <v>3000</v>
       </c>
       <c r="H6">
-        <v>12100</v>
+        <v>2100</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6" t="str">
-        <v>หน้าจอสัมผัสควบคุมเครื่องจักรความละเอียดสูง</v>
+        <v>ชุดแปลงไฟ AC To DC Power Unit สำหรับ New Box OR</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>prod-4</v>
+        <v>prod-or-box-01</v>
       </c>
       <c r="B7" t="str">
-        <v>ENG-PROGRAMMING</v>
+        <v>OR-BOX-01</v>
       </c>
       <c r="C7" t="str">
-        <v>ค่าบริการเขียนโปรแกรม PLC / SCADA &amp; HMI Design</v>
+        <v>Box Control</v>
       </c>
       <c r="D7" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E7" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F7" t="str">
-        <v>Man-Day</v>
+        <v>EA</v>
       </c>
       <c r="G7">
-        <v>15000</v>
+        <v>5500</v>
       </c>
       <c r="H7">
-        <v>7500</v>
+        <v>3800</v>
       </c>
       <c r="I7">
-        <v>999</v>
+        <v>20</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="str">
-        <v>วิศวกรผู้เชี่ยวชาญออกแบบและพัฒนาโปรแกรมควบคุมไลน์ผลิต</v>
+        <v>กล่องควบคุม Box Control สำหรับ New Box OR</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>prod-5</v>
+        <v>prod-or-acc-01</v>
       </c>
       <c r="B8" t="str">
-        <v>ENG-COMMISSION</v>
+        <v>OR-ACC-01</v>
       </c>
       <c r="C8" t="str">
-        <v>ค่าบริการทดสอบและติดตั้งระบบหน้างาน (On-site Commissioning)</v>
+        <v>Box Accessories</v>
       </c>
       <c r="D8" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E8" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F8" t="str">
-        <v>Man-Day</v>
+        <v>EA</v>
       </c>
       <c r="G8">
-        <v>12000</v>
+        <v>3500</v>
       </c>
       <c r="H8">
-        <v>6000</v>
+        <v>2400</v>
       </c>
       <c r="I8">
-        <v>999</v>
+        <v>20</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="str">
-        <v>ทดสอบความปลอดภัยและการทำงานของไลน์การผลิตหน้าโรงงาน</v>
+        <v>อุปกรณ์เสริมและสายเชื่อมต่อ Box Accessories</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>prod-trace-1</v>
+        <v>prod-or-sft-01</v>
       </c>
       <c r="B9" t="str">
-        <v>SW-TRACE-001</v>
+        <v>OR-SFT-01</v>
       </c>
       <c r="C9" t="str">
-        <v>Traceability Solenoid Line Software</v>
+        <v>Software</v>
       </c>
       <c r="D9" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E9" t="str">
         <v>SOFTWARE</v>
       </c>
       <c r="F9" t="str">
-        <v>Job</v>
+        <v>EA</v>
       </c>
       <c r="G9">
-        <v>2023419</v>
+        <v>5000</v>
       </c>
       <c r="H9">
-        <v>850000</v>
+        <v>3000</v>
       </c>
       <c r="I9">
-        <v>999</v>
+        <v>20</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="str">
-        <v>ซอฟต์แวร์ระบบตรวจสอบย้อนกลับ (Traceability) สายการผลิต Solenoid Line</v>
+        <v>ซอฟต์แวร์ควบคุมและโปรแกรมระบบ OR Board Software</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>prod-trace-2</v>
+        <v>prod-or-srv-01</v>
       </c>
       <c r="B10" t="str">
-        <v>SW-TRACE-002</v>
+        <v>OR-SRV-01</v>
       </c>
       <c r="C10" t="str">
-        <v>Traceability Solenoid Line Software เพิ่มเติม</v>
+        <v>ติดตั้ง &amp; ทดสอบระบบ (System Installation &amp; Testing)</v>
       </c>
       <c r="D10" t="str">
         <v>SERVICE</v>
       </c>
       <c r="E10" t="str">
-        <v>SOFTWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F10" t="str">
         <v>Job</v>
       </c>
       <c r="G10">
-        <v>150000</v>
+        <v>6000</v>
       </c>
       <c r="H10">
-        <v>60000</v>
+        <v>3500</v>
       </c>
       <c r="I10">
-        <v>999</v>
+        <v>20</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="str">
-        <v>ซอฟต์แวร์ฟังก์ชันเพิ่มเติม Traceability Solenoid Line</v>
+        <v>บริการติดตั้งและทดสอบระบบหน้างาน (System Installation &amp; Testing)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>prod-6</v>
+        <v>prod-1</v>
       </c>
       <c r="B11" t="str">
-        <v>MAINT-ANNUAL</v>
+        <v>PLC-S7-1200</v>
       </c>
       <c r="C11" t="str">
-        <v>สัญญาบริการบำรุงรักษาระบบอัตโนมัติรายปี (Annual PM Contract)</v>
+        <v>Siemens PLC SIMATIC S7-1200 CPU 1214C DC/DC/DC</v>
       </c>
       <c r="D11" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E11" t="str">
-        <v>MAINTENANCE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F11" t="str">
-        <v>สัญญา</v>
+        <v>เครื่อง</v>
       </c>
       <c r="G11">
-        <v>120000</v>
+        <v>18500</v>
       </c>
       <c r="H11">
-        <v>40000</v>
+        <v>13200</v>
       </c>
       <c r="I11">
-        <v>999</v>
+        <v>14</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K11" t="str">
-        <v>เข้าตรวจเช็คระบบรายไตรมาส (4 ครั้ง/ปี) พร้อม On-call 24 ชม.</v>
+        <v>โปรแกรมเมเบิลคอนโทรลเลอร์ 14 DI / 10 DO / 2 AI</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>prod-tsf-1</v>
+        <v>prod-2</v>
       </c>
       <c r="B12" t="str">
-        <v>TSF-ST-001</v>
+        <v>SERVO-750W</v>
       </c>
       <c r="C12" t="str">
-        <v>Station Stacker Foam</v>
+        <v>Omron Servo Motor &amp; Driver Set 750W 3000RPM</v>
       </c>
       <c r="D12" t="str">
         <v>PRODUCT</v>
@@ -1108,33 +1108,33 @@
         <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F12" t="str">
-        <v>SET</v>
+        <v>ชุด</v>
       </c>
       <c r="G12">
-        <v>765394</v>
+        <v>24500</v>
       </c>
       <c r="H12">
-        <v>420000</v>
+        <v>17800</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K12" t="str">
-        <v>ชุดสถานีเรียงโฟมอัตโนมัติ (Station Stacker Foam) เครื่อง TSF1 Auto pack LM1</v>
+        <v>ชุดเซอร์โวมอเตอร์และไดรเวอร์ความแม่นยำสูง</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>prod-tsf-2</v>
+        <v>prod-3</v>
       </c>
       <c r="B13" t="str">
-        <v>TSF-ST-002</v>
+        <v>HMI-KTP700</v>
       </c>
       <c r="C13" t="str">
-        <v>Station Open Bag &amp; Insert Foam</v>
+        <v>Siemens Touch Panel HMI KTP700 Basic 7 นิ้ว</v>
       </c>
       <c r="D13" t="str">
         <v>PRODUCT</v>
@@ -1143,398 +1143,398 @@
         <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F13" t="str">
-        <v>SET</v>
+        <v>เครื่อง</v>
       </c>
       <c r="G13">
-        <v>650215</v>
+        <v>16800</v>
       </c>
       <c r="H13">
-        <v>350000</v>
+        <v>12100</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K13" t="str">
-        <v>ชุดสถานีเปิดถุงและบรรจุโฟม (Station Open Bag &amp; Insert Foam)</v>
+        <v>หน้าจอสัมผัสควบคุมเครื่องจักรความละเอียดสูง</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>prod-tsf-3</v>
+        <v>prod-4</v>
       </c>
       <c r="B14" t="str">
-        <v>TSF-ST-003</v>
+        <v>ENG-PROGRAMMING</v>
       </c>
       <c r="C14" t="str">
-        <v>Station Pallet Stacker Foam</v>
+        <v>ค่าบริการเขียนโปรแกรม PLC / SCADA &amp; HMI Design</v>
       </c>
       <c r="D14" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E14" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F14" t="str">
-        <v>SET</v>
+        <v>Man-Day</v>
       </c>
       <c r="G14">
-        <v>690391</v>
+        <v>15000</v>
       </c>
       <c r="H14">
-        <v>380000</v>
+        <v>7500</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="str">
-        <v>ชุดสถานีเรียงพาเลทโฟม (Station Pallet Stacker Foam)</v>
+        <v>วิศวกรผู้เชี่ยวชาญออกแบบและพัฒนาโปรแกรมควบคุมไลน์ผลิต</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>prod-tsf-4</v>
+        <v>prod-5</v>
       </c>
       <c r="B15" t="str">
-        <v>TSF-ST-004</v>
+        <v>ENG-COMMISSION</v>
       </c>
       <c r="C15" t="str">
-        <v>Contron Box System</v>
+        <v>ค่าบริการทดสอบและติดตั้งระบบหน้างาน (On-site Commissioning)</v>
       </c>
       <c r="D15" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E15" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F15" t="str">
-        <v>SET</v>
+        <v>Man-Day</v>
       </c>
       <c r="G15">
-        <v>312000</v>
+        <v>12000</v>
       </c>
       <c r="H15">
-        <v>170000</v>
+        <v>6000</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="str">
-        <v>ตู้ควบคุมระบบไฟฟ้าและ PLC คอนโทรลเลอร์ (Control Box System)</v>
+        <v>ทดสอบความปลอดภัยและการทำงานของไลน์การผลิตหน้าโรงงาน</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>prod-tsf-5</v>
+        <v>prod-trace-1</v>
       </c>
       <c r="B16" t="str">
-        <v>TSF-SRV-001</v>
+        <v>SW-TRACE-001</v>
       </c>
       <c r="C16" t="str">
-        <v>Manpower and labor cost</v>
+        <v>Traceability Solenoid Line Software</v>
       </c>
       <c r="D16" t="str">
         <v>SERVICE</v>
       </c>
       <c r="E16" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>SOFTWARE</v>
       </c>
       <c r="F16" t="str">
-        <v>JOB</v>
+        <v>Job</v>
       </c>
       <c r="G16">
-        <v>575000</v>
+        <v>2023419</v>
       </c>
       <c r="H16">
-        <v>280000</v>
+        <v>850000</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16" t="str">
-        <v>ค่าแรงวิศวกร ประกอบ ติดตั้ง และทดสอบระบบ TSF1 Auto pack LM1</v>
+        <v>ซอฟต์แวร์ระบบตรวจสอบย้อนกลับ (Traceability) สายการผลิต Solenoid Line</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>prod-tsf-6</v>
+        <v>prod-trace-2</v>
       </c>
       <c r="B17" t="str">
-        <v>TSF-SRV-002</v>
+        <v>SW-TRACE-002</v>
       </c>
       <c r="C17" t="str">
-        <v>Transportation and accommodation</v>
+        <v>Traceability Solenoid Line Software เพิ่มเติม</v>
       </c>
       <c r="D17" t="str">
         <v>SERVICE</v>
       </c>
       <c r="E17" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>SOFTWARE</v>
       </c>
       <c r="F17" t="str">
-        <v>JOB</v>
+        <v>Job</v>
       </c>
       <c r="G17">
-        <v>45000</v>
+        <v>150000</v>
       </c>
       <c r="H17">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17" t="str">
-        <v>ค่าขนส่งเครื่องจักรและค่าที่พักเดินทางหน้างานโรงงานชลบุรี</v>
+        <v>ซอฟต์แวร์ฟังก์ชันเพิ่มเติม Traceability Solenoid Line</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>prod-tsf-7</v>
+        <v>prod-6</v>
       </c>
       <c r="B18" t="str">
-        <v>TSF-SRV-003</v>
+        <v>MAINT-ANNUAL</v>
       </c>
       <c r="C18" t="str">
-        <v>Profit / Project Management &amp; Warranty 1 year</v>
+        <v>สัญญาบริการบำรุงรักษาระบบอัตโนมัติรายปี (Annual PM Contract)</v>
       </c>
       <c r="D18" t="str">
         <v>SERVICE</v>
       </c>
       <c r="E18" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>MAINTENANCE</v>
       </c>
       <c r="F18" t="str">
-        <v>JOB</v>
+        <v>สัญญา</v>
       </c>
       <c r="G18">
-        <v>607600</v>
+        <v>120000</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18" t="str">
-        <v>ค่าบริหารโครงการ บริการหลังการขาย และรับประกันระบบ 1 ปี (Warranty 1 year)</v>
+        <v>เข้าตรวจเช็คระบบรายไตรมาส (4 ครั้ง/ปี) พร้อม On-call 24 ชม.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>prod-pnp-corr</v>
+        <v>prod-tsf-1</v>
       </c>
       <c r="B19" t="str">
-        <v>SW-TRACE-CORR</v>
+        <v>TSF-ST-001</v>
       </c>
       <c r="C19" t="str">
-        <v>Traceability Corrugating Line</v>
+        <v>Station Stacker Foam</v>
       </c>
       <c r="D19" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E19" t="str">
-        <v>SOFTWARE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F19" t="str">
-        <v>Job</v>
+        <v>SET</v>
       </c>
       <c r="G19">
-        <v>1005002.64</v>
+        <v>765394</v>
       </c>
       <c r="H19">
-        <v>450000</v>
+        <v>420000</v>
       </c>
       <c r="I19">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19" t="str">
-        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Corrugating Line โครงการ Fujipart (PO: 2505004)</v>
+        <v>ชุดสถานีเรียงโฟมอัตโนมัติ (Station Stacker Foam) เครื่อง TSF1 Auto pack LM1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>prod-pnp-wind</v>
+        <v>prod-tsf-2</v>
       </c>
       <c r="B20" t="str">
-        <v>SW-TRACE-WIND</v>
+        <v>TSF-ST-002</v>
       </c>
       <c r="C20" t="str">
-        <v>Traceability Winding Line</v>
+        <v>Station Open Bag &amp; Insert Foam</v>
       </c>
       <c r="D20" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E20" t="str">
-        <v>SOFTWARE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F20" t="str">
-        <v>Job</v>
+        <v>SET</v>
       </c>
       <c r="G20">
-        <v>707304.38</v>
+        <v>650215</v>
       </c>
       <c r="H20">
-        <v>320000</v>
+        <v>350000</v>
       </c>
       <c r="I20">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20" t="str">
-        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Winding Line โครงการ Fujipart (PO: 2505004)</v>
+        <v>ชุดสถานีเปิดถุงและบรรจุโฟม (Station Open Bag &amp; Insert Foam)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>prod-pnp-adh</v>
+        <v>prod-tsf-3</v>
       </c>
       <c r="B21" t="str">
-        <v>SW-TRACE-ADH</v>
+        <v>TSF-ST-003</v>
       </c>
       <c r="C21" t="str">
-        <v>Traceability Adhesive &amp; Spin Winding Line</v>
+        <v>Station Pallet Stacker Foam</v>
       </c>
       <c r="D21" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E21" t="str">
-        <v>SOFTWARE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F21" t="str">
-        <v>Job</v>
+        <v>SET</v>
       </c>
       <c r="G21">
-        <v>874426.94</v>
+        <v>690391</v>
       </c>
       <c r="H21">
-        <v>390000</v>
+        <v>380000</v>
       </c>
       <c r="I21">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" t="str">
-        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Adhesive &amp; Spin Winding Line โครงการ Fujipart (PO: 2505004)</v>
+        <v>ชุดสถานีเรียงพาเลทโฟม (Station Pallet Stacker Foam)</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>prod-pnp-df4</v>
+        <v>prod-tsf-4</v>
       </c>
       <c r="B22" t="str">
-        <v>SW-TRACE-DF4</v>
+        <v>TSF-ST-004</v>
       </c>
       <c r="C22" t="str">
-        <v>Traceability DF4 Line</v>
+        <v>Contron Box System</v>
       </c>
       <c r="D22" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E22" t="str">
-        <v>SOFTWARE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F22" t="str">
-        <v>Job</v>
+        <v>SET</v>
       </c>
       <c r="G22">
-        <v>1203060.14</v>
+        <v>312000</v>
       </c>
       <c r="H22">
-        <v>540000</v>
+        <v>170000</v>
       </c>
       <c r="I22">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22" t="str">
-        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต DF4 Line โครงการ Fujipart (PO: 2505004)</v>
+        <v>ตู้ควบคุมระบบไฟฟ้าและ PLC คอนโทรลเลอร์ (Control Box System)</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>prod-pnp-pack</v>
+        <v>prod-tsf-5</v>
       </c>
       <c r="B23" t="str">
-        <v>SW-TRACE-PACK</v>
+        <v>TSF-SRV-001</v>
       </c>
       <c r="C23" t="str">
-        <v>Traceability Packing Line</v>
+        <v>Manpower and labor cost</v>
       </c>
       <c r="D23" t="str">
         <v>SERVICE</v>
       </c>
       <c r="E23" t="str">
-        <v>SOFTWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F23" t="str">
-        <v>Job</v>
+        <v>JOB</v>
       </c>
       <c r="G23">
-        <v>553196.28</v>
+        <v>575000</v>
       </c>
       <c r="H23">
-        <v>250000</v>
+        <v>280000</v>
       </c>
       <c r="I23">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23" t="str">
-        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Packing Line โครงการ Fujipart (PO: 2505004)</v>
+        <v>ค่าแรงวิศวกร ประกอบ ติดตั้ง และทดสอบระบบ TSF1 Auto pack LM1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>prod-pnp-fab</v>
+        <v>prod-tsf-6</v>
       </c>
       <c r="B24" t="str">
-        <v>PNP-FAB-001</v>
+        <v>TSF-SRV-002</v>
       </c>
       <c r="C24" t="str">
-        <v>Standard and Feb Part (Zone 1-6)</v>
+        <v>Transportation and accommodation</v>
       </c>
       <c r="D24" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E24" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F24" t="str">
-        <v>Set</v>
+        <v>JOB</v>
       </c>
       <c r="G24">
-        <v>1140000</v>
+        <v>45000</v>
       </c>
       <c r="H24">
-        <v>650000</v>
+        <v>30000</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -1543,18 +1543,18 @@
         <v>0</v>
       </c>
       <c r="K24" t="str">
-        <v>ชุดโครงสร้างมาตรฐานและชิ้นงานประกอบ Fabricated Parts Zone 1-6 (PO: 2605001)</v>
+        <v>ค่าขนส่งเครื่องจักรและค่าที่พักเดินทางหน้างานโรงงานชลบุรี</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>prod-pnp-labor-z</v>
+        <v>prod-tsf-7</v>
       </c>
       <c r="B25" t="str">
-        <v>PNP-LAB-001</v>
+        <v>TSF-SRV-003</v>
       </c>
       <c r="C25" t="str">
-        <v>Manpower and Labor Cost (Zone 1-6)</v>
+        <v>Profit / Project Management &amp; Warranty 1 year</v>
       </c>
       <c r="D25" t="str">
         <v>SERVICE</v>
@@ -1563,13 +1563,13 @@
         <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F25" t="str">
-        <v>Job</v>
+        <v>JOB</v>
       </c>
       <c r="G25">
-        <v>670000</v>
+        <v>607600</v>
       </c>
       <c r="H25">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -1578,208 +1578,208 @@
         <v>0</v>
       </c>
       <c r="K25" t="str">
-        <v>ค่าแรงวิศวกรและทีมช่างประกอบ ติดตั้ง ทดสอบ Zone 1-6 (PO: 2605001)</v>
+        <v>ค่าบริหารโครงการ บริการหลังการขาย และรับประกันระบบ 1 ปี (Warranty 1 year)</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>prod-pnp-trans-z</v>
+        <v>prod-pnp-corr</v>
       </c>
       <c r="B26" t="str">
-        <v>PNP-LOG-001</v>
+        <v>SW-TRACE-CORR</v>
       </c>
       <c r="C26" t="str">
-        <v>Transportation and accommodation (Zone 1-6)</v>
+        <v>Traceability Corrugating Line</v>
       </c>
       <c r="D26" t="str">
         <v>SERVICE</v>
       </c>
       <c r="E26" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>SOFTWARE</v>
       </c>
       <c r="F26" t="str">
-        <v>EA</v>
+        <v>Job</v>
       </c>
       <c r="G26">
-        <v>45000</v>
+        <v>1005002.64</v>
       </c>
       <c r="H26">
-        <v>30000</v>
+        <v>450000</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26" t="str">
-        <v>ค่าขนส่งและที่พักเดินทางหน้างาน Zone 1-6 (PO: 2605001)</v>
+        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Corrugating Line โครงการ Fujipart (PO: 2505004)</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>prod-pnp-pm-z</v>
+        <v>prod-pnp-wind</v>
       </c>
       <c r="B27" t="str">
-        <v>PNP-PM-001</v>
+        <v>SW-TRACE-WIND</v>
       </c>
       <c r="C27" t="str">
-        <v>Project Management (Zone 1-6)</v>
+        <v>Traceability Winding Line</v>
       </c>
       <c r="D27" t="str">
         <v>SERVICE</v>
       </c>
       <c r="E27" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>SOFTWARE</v>
       </c>
       <c r="F27" t="str">
-        <v>EA</v>
+        <v>Job</v>
       </c>
       <c r="G27">
-        <v>556500</v>
+        <v>707304.38</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>320000</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27" t="str">
-        <v>ค่าบริหารจัดการโครงการ ควบคุมงาน และทดสอบระบบ Zone 1-6 (PO: 2605001)</v>
+        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Winding Line โครงการ Fujipart (PO: 2505004)</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>prod-pnp-fab-z7</v>
+        <v>prod-pnp-adh</v>
       </c>
       <c r="B28" t="str">
-        <v>PNP-FAB-002</v>
+        <v>SW-TRACE-ADH</v>
       </c>
       <c r="C28" t="str">
-        <v>Standard and Feb Part (Zone 7)</v>
+        <v>Traceability Adhesive &amp; Spin Winding Line</v>
       </c>
       <c r="D28" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E28" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>SOFTWARE</v>
       </c>
       <c r="F28" t="str">
-        <v>Set</v>
+        <v>Job</v>
       </c>
       <c r="G28">
-        <v>641000</v>
+        <v>874426.94</v>
       </c>
       <c r="H28">
-        <v>350000</v>
+        <v>390000</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28" t="str">
-        <v>ชุดโครงสร้างมาตรฐานและชิ้นงานประกอบ Fabricated Parts Zone 7 (PO: 2605002)</v>
+        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Adhesive &amp; Spin Winding Line โครงการ Fujipart (PO: 2505004)</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>prod-pnp-labor-z7</v>
+        <v>prod-pnp-df4</v>
       </c>
       <c r="B29" t="str">
-        <v>PNP-LAB-002</v>
+        <v>SW-TRACE-DF4</v>
       </c>
       <c r="C29" t="str">
-        <v>Manpower and Labor Cost (Zone 7)</v>
+        <v>Traceability DF4 Line</v>
       </c>
       <c r="D29" t="str">
         <v>SERVICE</v>
       </c>
       <c r="E29" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>SOFTWARE</v>
       </c>
       <c r="F29" t="str">
         <v>Job</v>
       </c>
       <c r="G29">
-        <v>220000</v>
+        <v>1203060.14</v>
       </c>
       <c r="H29">
-        <v>110000</v>
+        <v>540000</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29" t="str">
-        <v>ค่าแรงวิศวกรและทีมช่างประกอบ ติดตั้ง ทดสอบ Zone 7 (PO: 2605002)</v>
+        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต DF4 Line โครงการ Fujipart (PO: 2505004)</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>prod-pnp-trans-z7</v>
+        <v>prod-pnp-pack</v>
       </c>
       <c r="B30" t="str">
-        <v>PNP-LOG-002</v>
+        <v>SW-TRACE-PACK</v>
       </c>
       <c r="C30" t="str">
-        <v>Transportation and accommodation (Zone 7)</v>
+        <v>Traceability Packing Line</v>
       </c>
       <c r="D30" t="str">
         <v>SERVICE</v>
       </c>
       <c r="E30" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>SOFTWARE</v>
       </c>
       <c r="F30" t="str">
-        <v>EA</v>
+        <v>Job</v>
       </c>
       <c r="G30">
-        <v>45000</v>
+        <v>553196.28</v>
       </c>
       <c r="H30">
-        <v>30000</v>
+        <v>250000</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30" t="str">
-        <v>ค่าขนส่งและที่พักเดินทางหน้างาน Zone 7 (PO: 2605002)</v>
+        <v>ระบบซอฟต์แวร์ตรวจสอบย้อนกลับไลน์ผลิต Packing Line โครงการ Fujipart (PO: 2505004)</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>prod-pnp-pm-z7</v>
+        <v>prod-pnp-fab</v>
       </c>
       <c r="B31" t="str">
-        <v>PNP-PM-002</v>
+        <v>PNP-FAB-001</v>
       </c>
       <c r="C31" t="str">
-        <v>Project Management (Zone 7)</v>
+        <v>Standard and Feb Part (Zone 1-6)</v>
       </c>
       <c r="D31" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E31" t="str">
-        <v>ENGINEERING_SERVICE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F31" t="str">
-        <v>EA</v>
+        <v>Set</v>
       </c>
       <c r="G31">
-        <v>271800</v>
+        <v>1140000</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -1788,103 +1788,103 @@
         <v>0</v>
       </c>
       <c r="K31" t="str">
-        <v>ค่าบริหารจัดการโครงการ ควบคุมงาน และทดสอบระบบ Zone 7 (PO: 2605002)</v>
+        <v>ชุดโครงสร้างมาตรฐานและชิ้นงานประกอบ Fabricated Parts Zone 1-6 (PO: 2605001)</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>prod-pnp-plc-eth</v>
+        <v>prod-pnp-labor-z</v>
       </c>
       <c r="B32" t="str">
-        <v>PLC-ETH-001</v>
+        <v>PNP-LAB-001</v>
       </c>
       <c r="C32" t="str">
-        <v>PLC Control Board (Ethernet IP)</v>
+        <v>Manpower and Labor Cost (Zone 1-6)</v>
       </c>
       <c r="D32" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E32" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F32" t="str">
-        <v>EA</v>
+        <v>Job</v>
       </c>
       <c r="G32">
-        <v>35040</v>
+        <v>670000</v>
       </c>
       <c r="H32">
-        <v>22000</v>
+        <v>350000</v>
       </c>
       <c r="I32">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32" t="str">
-        <v>บอร์ดควบคุม PLC รองรับการเชื่อมต่อเครือข่าย Ethernet IP (PO: 2607001)</v>
+        <v>ค่าแรงวิศวกรและทีมช่างประกอบ ติดตั้ง ทดสอบ Zone 1-6 (PO: 2605001)</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>prod-pnp-sub-plc</v>
+        <v>prod-pnp-trans-z</v>
       </c>
       <c r="B33" t="str">
-        <v>PLC-SUB-001</v>
+        <v>PNP-LOG-001</v>
       </c>
       <c r="C33" t="str">
-        <v>Sub PLC Box + Aceessories</v>
+        <v>Transportation and accommodation (Zone 1-6)</v>
       </c>
       <c r="D33" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E33" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F33" t="str">
         <v>EA</v>
       </c>
       <c r="G33">
-        <v>26000</v>
+        <v>45000</v>
       </c>
       <c r="H33">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33" t="str">
-        <v>ตู้ Sub PLC พร้อมอุปกรณ์ส่วนควบ Accessories (PO: 2607001)</v>
+        <v>ค่าขนส่งและที่พักเดินทางหน้างาน Zone 1-6 (PO: 2605001)</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>prod-pnp-rack-pc</v>
+        <v>prod-pnp-pm-z</v>
       </c>
       <c r="B34" t="str">
-        <v>PC-RACK-001</v>
+        <v>PNP-PM-001</v>
       </c>
       <c r="C34" t="str">
-        <v>Rack PC Center</v>
+        <v>Project Management (Zone 1-6)</v>
       </c>
       <c r="D34" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E34" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F34" t="str">
         <v>EA</v>
       </c>
       <c r="G34">
-        <v>12000</v>
+        <v>556500</v>
       </c>
       <c r="H34">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>1</v>
@@ -1893,33 +1893,33 @@
         <v>0</v>
       </c>
       <c r="K34" t="str">
-        <v>ตู้แร็คศูนย์คอมพิวเตอร์และเซิร์ฟเวอร์ Rack PC Center (PO: 2607001)</v>
+        <v>ค่าบริหารจัดการโครงการ ควบคุมงาน และทดสอบระบบ Zone 1-6 (PO: 2605001)</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>prod-pnp-plc-dc</v>
+        <v>prod-pnp-fab-z7</v>
       </c>
       <c r="B35" t="str">
-        <v>PLC-DC-001</v>
+        <v>PNP-FAB-002</v>
       </c>
       <c r="C35" t="str">
-        <v>PLC Data Center Line</v>
+        <v>Standard and Feb Part (Zone 7)</v>
       </c>
       <c r="D35" t="str">
-        <v>SERVICE</v>
+        <v>PRODUCT</v>
       </c>
       <c r="E35" t="str">
-        <v>SOFTWARE</v>
+        <v>AUTOMATION_HARDWARE</v>
       </c>
       <c r="F35" t="str">
-        <v>EA</v>
+        <v>Set</v>
       </c>
       <c r="G35">
-        <v>150000</v>
+        <v>641000</v>
       </c>
       <c r="H35">
-        <v>80000</v>
+        <v>350000</v>
       </c>
       <c r="I35">
         <v>1</v>
@@ -1928,33 +1928,33 @@
         <v>0</v>
       </c>
       <c r="K35" t="str">
-        <v>ระบบศูนย์รวมและประมวลผลข้อมูลสายการผลิต PLC Data Center Line (PO: 2607001)</v>
+        <v>ชุดโครงสร้างมาตรฐานและชิ้นงานประกอบ Fabricated Parts Zone 7 (PO: 2605002)</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>prod-pnp-struct-sup</v>
+        <v>prod-pnp-labor-z7</v>
       </c>
       <c r="B36" t="str">
-        <v>STR-SUP-001</v>
+        <v>PNP-LAB-002</v>
       </c>
       <c r="C36" t="str">
-        <v>Stucture Support</v>
+        <v>Manpower and Labor Cost (Zone 7)</v>
       </c>
       <c r="D36" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E36" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F36" t="str">
-        <v>EA</v>
+        <v>Job</v>
       </c>
       <c r="G36">
-        <v>20000</v>
+        <v>220000</v>
       </c>
       <c r="H36">
-        <v>10000</v>
+        <v>110000</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -1963,33 +1963,33 @@
         <v>0</v>
       </c>
       <c r="K36" t="str">
-        <v>ชุดโครงสร้างรองรับและฐานยึดอุปกรณ์ Structure Support (PO: 2607001)</v>
+        <v>ค่าแรงวิศวกรและทีมช่างประกอบ ติดตั้ง ทดสอบ Zone 7 (PO: 2605002)</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>prod-pnp-pc-center</v>
+        <v>prod-pnp-trans-z7</v>
       </c>
       <c r="B37" t="str">
-        <v>PC-CTR-001</v>
+        <v>PNP-LOG-002</v>
       </c>
       <c r="C37" t="str">
-        <v>PC Center</v>
+        <v>Transportation and accommodation (Zone 7)</v>
       </c>
       <c r="D37" t="str">
-        <v>PRODUCT</v>
+        <v>SERVICE</v>
       </c>
       <c r="E37" t="str">
-        <v>AUTOMATION_HARDWARE</v>
+        <v>ENGINEERING_SERVICE</v>
       </c>
       <c r="F37" t="str">
         <v>EA</v>
       </c>
       <c r="G37">
-        <v>123000</v>
+        <v>45000</v>
       </c>
       <c r="H37">
-        <v>75000</v>
+        <v>30000</v>
       </c>
       <c r="I37">
         <v>1</v>
@@ -1998,18 +1998,18 @@
         <v>0</v>
       </c>
       <c r="K37" t="str">
-        <v>เครื่องคอมพิวเตอร์แม่ข่ายประมวลผล PC Center (PO: 2607001)</v>
+        <v>ค่าขนส่งและที่พักเดินทางหน้างาน Zone 7 (PO: 2605002)</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>prod-pnp-pm-2607</v>
+        <v>prod-pnp-pm-z7</v>
       </c>
       <c r="B38" t="str">
-        <v>PNP-PM-2607</v>
+        <v>PNP-PM-002</v>
       </c>
       <c r="C38" t="str">
-        <v>Project Management (PO: 2607001)</v>
+        <v>Project Management (Zone 7)</v>
       </c>
       <c r="D38" t="str">
         <v>SERVICE</v>
@@ -2021,31 +2021,276 @@
         <v>EA</v>
       </c>
       <c r="G38">
+        <v>271800</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" t="str">
+        <v>ค่าบริหารจัดการโครงการ ควบคุมงาน และทดสอบระบบ Zone 7 (PO: 2605002)</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>prod-pnp-plc-eth</v>
+      </c>
+      <c r="B39" t="str">
+        <v>PLC-ETH-001</v>
+      </c>
+      <c r="C39" t="str">
+        <v>PLC Control Board (Ethernet IP)</v>
+      </c>
+      <c r="D39" t="str">
+        <v>PRODUCT</v>
+      </c>
+      <c r="E39" t="str">
+        <v>AUTOMATION_HARDWARE</v>
+      </c>
+      <c r="F39" t="str">
+        <v>EA</v>
+      </c>
+      <c r="G39">
+        <v>35040</v>
+      </c>
+      <c r="H39">
+        <v>22000</v>
+      </c>
+      <c r="I39">
+        <v>21</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="str">
+        <v>บอร์ดควบคุม PLC รองรับการเชื่อมต่อเครือข่าย Ethernet IP (PO: 2607001)</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>prod-pnp-sub-plc</v>
+      </c>
+      <c r="B40" t="str">
+        <v>PLC-SUB-001</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Sub PLC Box + Aceessories</v>
+      </c>
+      <c r="D40" t="str">
+        <v>PRODUCT</v>
+      </c>
+      <c r="E40" t="str">
+        <v>AUTOMATION_HARDWARE</v>
+      </c>
+      <c r="F40" t="str">
+        <v>EA</v>
+      </c>
+      <c r="G40">
+        <v>26000</v>
+      </c>
+      <c r="H40">
+        <v>15000</v>
+      </c>
+      <c r="I40">
+        <v>6</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="str">
+        <v>ตู้ Sub PLC พร้อมอุปกรณ์ส่วนควบ Accessories (PO: 2607001)</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>prod-pnp-rack-pc</v>
+      </c>
+      <c r="B41" t="str">
+        <v>PC-RACK-001</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Rack PC Center</v>
+      </c>
+      <c r="D41" t="str">
+        <v>PRODUCT</v>
+      </c>
+      <c r="E41" t="str">
+        <v>AUTOMATION_HARDWARE</v>
+      </c>
+      <c r="F41" t="str">
+        <v>EA</v>
+      </c>
+      <c r="G41">
+        <v>12000</v>
+      </c>
+      <c r="H41">
+        <v>7000</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="str">
+        <v>ตู้แร็คศูนย์คอมพิวเตอร์และเซิร์ฟเวอร์ Rack PC Center (PO: 2607001)</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>prod-pnp-plc-dc</v>
+      </c>
+      <c r="B42" t="str">
+        <v>PLC-DC-001</v>
+      </c>
+      <c r="C42" t="str">
+        <v>PLC Data Center Line</v>
+      </c>
+      <c r="D42" t="str">
+        <v>SERVICE</v>
+      </c>
+      <c r="E42" t="str">
+        <v>SOFTWARE</v>
+      </c>
+      <c r="F42" t="str">
+        <v>EA</v>
+      </c>
+      <c r="G42">
+        <v>150000</v>
+      </c>
+      <c r="H42">
+        <v>80000</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="str">
+        <v>ระบบศูนย์รวมและประมวลผลข้อมูลสายการผลิต PLC Data Center Line (PO: 2607001)</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>prod-pnp-struct-sup</v>
+      </c>
+      <c r="B43" t="str">
+        <v>STR-SUP-001</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Stucture Support</v>
+      </c>
+      <c r="D43" t="str">
+        <v>PRODUCT</v>
+      </c>
+      <c r="E43" t="str">
+        <v>AUTOMATION_HARDWARE</v>
+      </c>
+      <c r="F43" t="str">
+        <v>EA</v>
+      </c>
+      <c r="G43">
+        <v>20000</v>
+      </c>
+      <c r="H43">
+        <v>10000</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" t="str">
+        <v>ชุดโครงสร้างรองรับและฐานยึดอุปกรณ์ Structure Support (PO: 2607001)</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>prod-pnp-pc-center</v>
+      </c>
+      <c r="B44" t="str">
+        <v>PC-CTR-001</v>
+      </c>
+      <c r="C44" t="str">
+        <v>PC Center</v>
+      </c>
+      <c r="D44" t="str">
+        <v>PRODUCT</v>
+      </c>
+      <c r="E44" t="str">
+        <v>AUTOMATION_HARDWARE</v>
+      </c>
+      <c r="F44" t="str">
+        <v>EA</v>
+      </c>
+      <c r="G44">
+        <v>123000</v>
+      </c>
+      <c r="H44">
+        <v>75000</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" t="str">
+        <v>เครื่องคอมพิวเตอร์แม่ข่ายประมวลผล PC Center (PO: 2607001)</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>prod-pnp-pm-2607</v>
+      </c>
+      <c r="B45" t="str">
+        <v>PNP-PM-2607</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Project Management (PO: 2607001)</v>
+      </c>
+      <c r="D45" t="str">
+        <v>SERVICE</v>
+      </c>
+      <c r="E45" t="str">
+        <v>ENGINEERING_SERVICE</v>
+      </c>
+      <c r="F45" t="str">
+        <v>EA</v>
+      </c>
+      <c r="G45">
         <v>573552</v>
       </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38">
-        <v>1</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38" t="str">
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" t="str">
         <v>ค่าบริหารจัดการโครงการ ควบคุมงาน และทดสอบระบบ (PO: 2607001)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3163,16 +3408,57 @@
         <v>จัดส่งที่: บริษัท วอร์สเกต จำกัด (สำนักงานใหญ่) หมู่บ้าน พฤกษาวิลล์ 46/1 เลขที่ 50/8 หมู่ 4 ตำบลคลองสาม อำเภอคลองหลวง จังหวัดปทุมธานี 12120 โทร. 083-066-7309</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>doc-pnp-qt-2609001</v>
+      </c>
+      <c r="B28" t="str">
+        <v>QUOTATION</v>
+      </c>
+      <c r="C28" t="str">
+        <v>QT-2609-001</v>
+      </c>
+      <c r="D28" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="E28" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="I28">
+        <v>840000</v>
+      </c>
+      <c r="J28">
+        <v>58800</v>
+      </c>
+      <c r="K28">
+        <v>898800</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>898800</v>
+      </c>
+      <c r="N28" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v>เสนอราคาโครงการ Service Repair &amp; Maintenance OR Board (New Box OR) | ยืนยันราคาภายใน 30 วัน | เงื่อนไขการชำระเงิน: เครดิต 30 วัน</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P28"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5858,9 +6144,212 @@
         <v>0</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>QT-2609-001</v>
+      </c>
+      <c r="B95" t="str">
+        <v>QUOTATION</v>
+      </c>
+      <c r="C95" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v>PC Board สำหรับ New Box OR</v>
+      </c>
+      <c r="H95">
+        <v>20</v>
+      </c>
+      <c r="I95" t="str">
+        <v>EA</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>QT-2609-001</v>
+      </c>
+      <c r="B96" t="str">
+        <v>QUOTATION</v>
+      </c>
+      <c r="C96" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="E96">
+        <v>2</v>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v>Board Digital Input / Output สำหรับ New Box OR</v>
+      </c>
+      <c r="H96">
+        <v>20</v>
+      </c>
+      <c r="I96" t="str">
+        <v>EA</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>QT-2609-001</v>
+      </c>
+      <c r="B97" t="str">
+        <v>QUOTATION</v>
+      </c>
+      <c r="C97" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="E97">
+        <v>3</v>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v>ชุดแปลงไฟ AC To DC Power Unit สำหรับ New Box OR</v>
+      </c>
+      <c r="H97">
+        <v>20</v>
+      </c>
+      <c r="I97" t="str">
+        <v>EA</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>QT-2609-001</v>
+      </c>
+      <c r="B98" t="str">
+        <v>QUOTATION</v>
+      </c>
+      <c r="C98" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="E98">
+        <v>4</v>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v>กล่องควบคุม Box Control สำหรับ New Box OR</v>
+      </c>
+      <c r="H98">
+        <v>20</v>
+      </c>
+      <c r="I98" t="str">
+        <v>EA</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>QT-2609-001</v>
+      </c>
+      <c r="B99" t="str">
+        <v>QUOTATION</v>
+      </c>
+      <c r="C99" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="E99">
+        <v>5</v>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v>อุปกรณ์เสริมและสายเชื่อมต่อ Box Accessories</v>
+      </c>
+      <c r="H99">
+        <v>20</v>
+      </c>
+      <c r="I99" t="str">
+        <v>EA</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>QT-2609-001</v>
+      </c>
+      <c r="B100" t="str">
+        <v>QUOTATION</v>
+      </c>
+      <c r="C100" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="E100">
+        <v>6</v>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v>ซอฟต์แวร์ควบคุมและโปรแกรมระบบ OR Board Software</v>
+      </c>
+      <c r="H100">
+        <v>20</v>
+      </c>
+      <c r="I100" t="str">
+        <v>EA</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>QT-2609-001</v>
+      </c>
+      <c r="B101" t="str">
+        <v>QUOTATION</v>
+      </c>
+      <c r="C101" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="E101">
+        <v>7</v>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v>บริการติดตั้งและทดสอบระบบหน้างาน (System Installation &amp; Testing)</v>
+      </c>
+      <c r="H101">
+        <v>20</v>
+      </c>
+      <c r="I101" t="str">
+        <v>Job</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/backups/warsgate_accounting_backup_latest.xlsx
+++ b/backups/warsgate_accounting_backup_latest.xlsx
@@ -3457,7 +3457,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3550,7 +3550,7 @@
         <v>PENDING</v>
       </c>
       <c r="O2" t="str">
-        <v>อ้างอิงใบสั่งซื้อ PO:2505004 บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+        <v>อ้างอิงใบสั่งซื้อ PO:2505004 บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด [วางบิลงวดที่ 2 เรียบร้อยแล้ว 50% รอชำระเงิน]</v>
       </c>
     </row>
     <row r="3">
@@ -3641,7 +3641,7 @@
         <v>252049.2</v>
       </c>
       <c r="N4" t="str">
-        <v>PENDING</v>
+        <v>PAID</v>
       </c>
       <c r="O4" t="str">
         <v>อ้างอิงใบสั่งซื้อ PO:2605002 บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
@@ -3688,7 +3688,7 @@
         <v>516061</v>
       </c>
       <c r="N5" t="str">
-        <v>PENDING</v>
+        <v>PAID</v>
       </c>
       <c r="O5" t="str">
         <v>อ้างอิงใบสั่งซื้อ PO: 2506001 บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
@@ -3735,7 +3735,7 @@
         <v>258030.5</v>
       </c>
       <c r="N6" t="str">
-        <v>PENDING</v>
+        <v>PAID</v>
       </c>
       <c r="O6" t="str">
         <v>อ้างอิงใบสั่งซื้อ PO: 2605001 บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
@@ -3782,7 +3782,7 @@
         <v>126024.6</v>
       </c>
       <c r="N7" t="str">
-        <v>PENDING</v>
+        <v>PAID</v>
       </c>
       <c r="O7" t="str">
         <v>อ้างอิงใบสั่งซื้อ PO:2605002 บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
@@ -3852,7 +3852,7 @@
         <v>2026-01-14</v>
       </c>
       <c r="F9" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="G9" t="str">
         <v>PO252155</v>
@@ -4119,395 +4119,395 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>doc-inv-001</v>
+        <v>doc-tsf-qt-252155</v>
       </c>
       <c r="B15" t="str">
-        <v>INVOICE</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C15" t="str">
-        <v>INV-202607-001</v>
+        <v>QT-2512-2155</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-07-15</v>
+        <v>2025-12-24</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-14</v>
+        <v>2026-01-23</v>
       </c>
       <c r="F15" t="str">
         <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>PO252155</v>
       </c>
       <c r="H15" t="str">
         <v/>
       </c>
       <c r="I15">
-        <v>237500</v>
+        <v>3645600</v>
       </c>
       <c r="J15">
-        <v>16625</v>
+        <v>248192</v>
       </c>
       <c r="K15">
-        <v>254125</v>
+        <v>3793792</v>
       </c>
       <c r="L15">
-        <v>4350</v>
+        <v>106368</v>
       </c>
       <c r="M15">
-        <v>249775</v>
+        <v>3687424</v>
       </c>
       <c r="N15" t="str">
-        <v>PENDING</v>
+        <v>APPROVED</v>
       </c>
       <c r="O15" t="str">
-        <v>กำหนดยอดชำระภายใน 30 วัน โอนเข้าบัญชี KBANK บจก. วอร์สเกต ออโตเมชั่น</v>
+        <v>โครงการ TSF1 Auto pack LM1 (TSF1-LM1_Auto pack machine - K.Alongkorn) ตามใบสั่งซื้อ PO: PO252155 (Ref: CAP250095/) เงื่อนไขชำระเงิน 3 งวด: 1. 40% Down [฿1,517,516.80], 2. 30% After Process Work [฿1,138,137.60], 3. 30% After Complete Work [฿1,138,137.60] รับประกัน 1 ปี</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>doc-qt-001</v>
+        <v>doc-pnp-qt-2505004</v>
       </c>
       <c r="B16" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C16" t="str">
-        <v>QT-202607-002</v>
+        <v>QT-2505-004</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-07-28</v>
+        <v>2025-05-07</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-27</v>
+        <v>2025-06-06</v>
       </c>
       <c r="F16" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>2505004</v>
       </c>
       <c r="H16" t="str">
         <v/>
       </c>
       <c r="I16">
-        <v>156000</v>
+        <v>4342990.38</v>
       </c>
       <c r="J16">
-        <v>10920</v>
+        <v>304009.33</v>
       </c>
       <c r="K16">
-        <v>166920</v>
+        <v>4646999.71</v>
       </c>
       <c r="L16">
-        <v>1800</v>
+        <v>130289.71</v>
       </c>
       <c r="M16">
-        <v>165120</v>
+        <v>4516710</v>
       </c>
       <c r="N16" t="str">
         <v>APPROVED</v>
       </c>
       <c r="O16" t="str">
-        <v>เสนอราคา ยืนยันราคาภายใน 30 วัน</v>
+        <v>โครงการพัฒนาระบบ Traceability 5 ไลน์ผลิต (Fujipart Thailand Co., Ltd.) ตามใบสั่งซื้อลูกค้า PO: 2505004 ลงวันที่ 7 พ.ค. 2568 (เงื่อนไขชำระเงิน: ชำระเมื่อส่งของครบตามใบสั่งซื้อ, วางบิลวันที่ 1-25 ของทุกเดือน, ใบกำกับภาษี + สำเนา 5 ใบ)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>doc-po-001</v>
+        <v>doc-pnp-qt-2605001</v>
       </c>
       <c r="B17" t="str">
-        <v>PURCHASE_ORDER</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C17" t="str">
-        <v>PO-202607-001</v>
+        <v>QT-2605-001</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-07-20</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-05</v>
+        <v>2026-06-01</v>
       </c>
       <c r="F17" t="str">
-        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>2605001</v>
       </c>
       <c r="H17" t="str">
         <v/>
       </c>
       <c r="I17">
-        <v>132000</v>
+        <v>2411500</v>
       </c>
       <c r="J17">
-        <v>9240</v>
+        <v>168805</v>
       </c>
       <c r="K17">
-        <v>141240</v>
+        <v>2580305</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>72345</v>
       </c>
       <c r="M17">
-        <v>141240</v>
+        <v>2507960</v>
       </c>
       <c r="N17" t="str">
         <v>APPROVED</v>
       </c>
       <c r="O17" t="str">
-        <v>จัดส่งที่คลังสินค้า สมุทรปราการ</v>
+        <v>โครงการ Zone 1-6 (Fujipart Thailand) ตามใบสั่งซื้อ PO: 2605001 ลงวันที่ 2 พ.ค. 2569 (เงื่อนไข: ชำระค่าสินค้าเมื่อส่งของครบตามใบสั่งซื้อ, วางบิลวันที่ 1-25 ของทุกเดือน, ใบกำกับภาษี + สำเนา 5 ใบ)</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>doc-tsf-qt-252155</v>
+        <v>doc-pnp-qt-2605002</v>
       </c>
       <c r="B18" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C18" t="str">
-        <v>QT-2512-2155</v>
+        <v>QT-2605-002</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-12-24</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-01-23</v>
+        <v>2026-06-01</v>
       </c>
       <c r="F18" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="G18" t="str">
-        <v>PO252155</v>
+        <v>2605002</v>
       </c>
       <c r="H18" t="str">
         <v/>
       </c>
       <c r="I18">
-        <v>3645600</v>
+        <v>1177800</v>
       </c>
       <c r="J18">
-        <v>248192</v>
+        <v>82446</v>
       </c>
       <c r="K18">
-        <v>3793792</v>
+        <v>1260246</v>
       </c>
       <c r="L18">
-        <v>106368</v>
+        <v>35334</v>
       </c>
       <c r="M18">
-        <v>3687424</v>
+        <v>1224912</v>
       </c>
       <c r="N18" t="str">
         <v>APPROVED</v>
       </c>
       <c r="O18" t="str">
-        <v>โครงการ TSF1 Auto pack LM1 (TSF1-LM1_Auto pack machine - K.Alongkorn) ตามใบสั่งซื้อ PO: PO252155 (Ref: CAP250095/) เงื่อนไขชำระเงิน 3 งวด: 1. 40% Down [฿1,517,516.80], 2. 30% After Process Work [฿1,138,137.60], 3. 30% After Complete Work [฿1,138,137.60] รับประกัน 1 ปี</v>
+        <v>โครงการ Zone 7 (Fujipart Thailand) ตามใบสั่งซื้อ PO: 2605002 ลงวันที่ 2 พ.ค. 2569 (เงื่อนไข: ชำระค่าสินค้าเมื่อส่งของครบตามใบสั่งซื้อ, วางบิลวันที่ 1-25 ของทุกเดือน, ใบกำกับภาษี + สำเนา 5 ใบ)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>doc-pnp-qt-2505004</v>
+        <v>doc-pnp-rec-2605002-1</v>
       </c>
       <c r="B19" t="str">
-        <v>QUOTATION</v>
+        <v>RECEIPT</v>
       </c>
       <c r="C19" t="str">
-        <v>QT-2505-004</v>
+        <v>REC-2605-002/1</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-05-07</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E19" t="str">
-        <v>2025-06-06</v>
+        <v>2026-05-25</v>
       </c>
       <c r="F19" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="G19" t="str">
-        <v>2505004</v>
+        <v>2605002</v>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19">
-        <v>4342990.38</v>
+        <v>353340</v>
       </c>
       <c r="J19">
-        <v>304009.33</v>
+        <v>24733.8</v>
       </c>
       <c r="K19">
-        <v>4646999.71</v>
+        <v>378073.8</v>
       </c>
       <c r="L19">
-        <v>130289.71</v>
+        <v>10600.2</v>
       </c>
       <c r="M19">
-        <v>4516710</v>
+        <v>367473.6</v>
       </c>
       <c r="N19" t="str">
-        <v>APPROVED</v>
+        <v>PAID</v>
       </c>
       <c r="O19" t="str">
-        <v>โครงการพัฒนาระบบ Traceability 5 ไลน์ผลิต (Fujipart Thailand Co., Ltd.) ตามใบสั่งซื้อลูกค้า PO: 2505004 ลงวันที่ 7 พ.ค. 2568 (เงื่อนไขชำระเงิน: ชำระเมื่อส่งของครบตามใบสั่งซื้อ, วางบิลวันที่ 1-25 ของทุกเดือน, ใบกำกับภาษี + สำเนา 5 ใบ)</v>
+        <v>รับชำระเงินงวดที่ 1 (30% Downpayment) โครงการ Zone 7 (Fujipart) ตามใบสั่งซื้อ PO: 2605002 โอนเข้าบัญชี KBANK บจก. วอร์สเกต</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>doc-pnp-qt-2605001</v>
+        <v>doc-pnp-qt-2607001</v>
       </c>
       <c r="B20" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C20" t="str">
-        <v>QT-2605-001</v>
+        <v>QT-2607-001</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-02</v>
+        <v>2026-07-17</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-06-01</v>
+        <v>2026-08-16</v>
       </c>
       <c r="F20" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="G20" t="str">
-        <v>2605001</v>
+        <v>2607001</v>
       </c>
       <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20">
-        <v>2411500</v>
+        <v>2439832</v>
       </c>
       <c r="J20">
-        <v>168805</v>
+        <v>170788.24</v>
       </c>
       <c r="K20">
-        <v>2580305</v>
+        <v>2610620.24</v>
       </c>
       <c r="L20">
-        <v>72345</v>
+        <v>73194.96</v>
       </c>
       <c r="M20">
-        <v>2507960</v>
+        <v>2537425.28</v>
       </c>
       <c r="N20" t="str">
         <v>APPROVED</v>
       </c>
       <c r="O20" t="str">
-        <v>โครงการ Zone 1-6 (Fujipart Thailand) ตามใบสั่งซื้อ PO: 2605001 ลงวันที่ 2 พ.ค. 2569 (เงื่อนไข: ชำระค่าสินค้าเมื่อส่งของครบตามใบสั่งซื้อ, วางบิลวันที่ 1-25 ของทุกเดือน, ใบกำกับภาษี + สำเนา 5 ใบ)</v>
+        <v>โครงการตามใบสั่งซื้อ PO: 2607001 ลงวันที่ 17 ก.ค. 2569 (รวมส่วนลดพิเศษ ฿45,560.00, ชำระค่าสินค้าเมื่อส่งของครบตามใบสั่งซื้อ, วางบิลวันที่ 1-25 ของทุกเดือน, ใบกำกับภาษี + สำเนา 5 ใบ)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>doc-pnp-qt-2605002</v>
+        <v>doc-pnp-do-2607001</v>
       </c>
       <c r="B21" t="str">
-        <v>QUOTATION</v>
+        <v>DELIVERY_ORDER</v>
       </c>
       <c r="C21" t="str">
-        <v>QT-2605-002</v>
+        <v>DO-2608-001</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-02</v>
+        <v>2026-08-20</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-06-01</v>
+        <v>2026-08-20</v>
       </c>
       <c r="F21" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="G21" t="str">
-        <v>2605002</v>
+        <v>2607001</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>รายการ Part ที่จะจัดส่งของ Line ADC โครงการ PLC Control Board (Ethernet IP)</v>
       </c>
       <c r="I21">
-        <v>1177800</v>
+        <v>1196840</v>
       </c>
       <c r="J21">
-        <v>82446</v>
+        <v>83778.8</v>
       </c>
       <c r="K21">
-        <v>1260246</v>
+        <v>1280618.8</v>
       </c>
       <c r="L21">
-        <v>35334</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>1224912</v>
+        <v>1280618.8</v>
       </c>
       <c r="N21" t="str">
         <v>APPROVED</v>
       </c>
       <c r="O21" t="str">
-        <v>โครงการ Zone 7 (Fujipart Thailand) ตามใบสั่งซื้อ PO: 2605002 ลงวันที่ 2 พ.ค. 2569 (เงื่อนไข: ชำระค่าสินค้าเมื่อส่งของครบตามใบสั่งซื้อ, วางบิลวันที่ 1-25 ของทุกเดือน, ใบกำกับภาษี + สำเนา 5 ใบ)</v>
+        <v>ใบส่งของชั่วคราว / ใบส่งสินค้า ตามใบสั่งซื้อ PO: 2607001 รายการ Part ที่จัดส่งของ Line ADC โครงการ PLC Control Board (Ethernet IP) เพื่อตรวจรับหน้างานโรงงานชลบุรี</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>doc-pnp-rec-2605002-1</v>
+        <v>doc-pnp-inv-2607001</v>
       </c>
       <c r="B22" t="str">
-        <v>RECEIPT</v>
+        <v>INVOICE</v>
       </c>
       <c r="C22" t="str">
-        <v>REC-2605-002/1</v>
+        <v>INV-2608-001</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-25</v>
+        <v>2026-08-20</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-05-25</v>
+        <v>2026-09-19</v>
       </c>
       <c r="F22" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="G22" t="str">
-        <v>2605002</v>
+        <v>2607001</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>รายการ Part ที่จะจัดส่งของ Line ADC โครงการ PLC Control Board (Ethernet IP)</v>
       </c>
       <c r="I22">
-        <v>353340</v>
+        <v>1219916</v>
       </c>
       <c r="J22">
-        <v>24733.8</v>
+        <v>85394.12</v>
       </c>
       <c r="K22">
-        <v>378073.8</v>
+        <v>1305310.12</v>
       </c>
       <c r="L22">
-        <v>10600.2</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>367473.6</v>
+        <v>1305310.12</v>
       </c>
       <c r="N22" t="str">
-        <v>PAID</v>
+        <v>PENDING</v>
       </c>
       <c r="O22" t="str">
-        <v>รับชำระเงินงวดที่ 1 (30% Downpayment) โครงการ Zone 7 (Fujipart) ตามใบสั่งซื้อ PO: 2605002 โอนเข้าบัญชี KBANK บจก. วอร์สเกต</v>
+        <v>ใบแจ้งหนี้ / ใบวางบิลงวดที่ 1 (50%) ตามใบสั่งซื้อ PO: 2607001 โครงการ Line ADC &amp; Data Center (เงื่อนไขการชำระเงิน: เครดิต 30 วัน ครบกำหนด 19 ก.ย. 2569 โอนเข้าบัญชี KBANK บจก. วอร์สเกต)</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>doc-pnp-qt-2607001</v>
+        <v>doc-pnp-tax-2607001</v>
       </c>
       <c r="B23" t="str">
-        <v>QUOTATION</v>
+        <v>TAX_INVOICE</v>
       </c>
       <c r="C23" t="str">
-        <v>QT-2607-001</v>
+        <v>TAX-2608-001</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-07-17</v>
+        <v>2026-08-20</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-16</v>
+        <v>2026-09-19</v>
       </c>
       <c r="F23" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
@@ -4516,189 +4516,189 @@
         <v>2607001</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>รายการ Part ที่จะจัดส่งของ Line ADC โครงการ PLC Control Board (Ethernet IP)</v>
       </c>
       <c r="I23">
-        <v>2439832</v>
+        <v>1196840</v>
       </c>
       <c r="J23">
-        <v>170788.24</v>
+        <v>83778.8</v>
       </c>
       <c r="K23">
-        <v>2610620.24</v>
+        <v>1280618.8</v>
       </c>
       <c r="L23">
-        <v>73194.96</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>2537425.28</v>
+        <v>1280618.8</v>
       </c>
       <c r="N23" t="str">
         <v>APPROVED</v>
       </c>
       <c r="O23" t="str">
-        <v>โครงการตามใบสั่งซื้อ PO: 2607001 ลงวันที่ 17 ก.ค. 2569 (รวมส่วนลดพิเศษ ฿45,560.00, ชำระค่าสินค้าเมื่อส่งของครบตามใบสั่งซื้อ, วางบิลวันที่ 1-25 ของทุกเดือน, ใบกำกับภาษี + สำเนา 5 ใบ)</v>
+        <v>ใบกำกับภาษี ตามใบสั่งซื้อ PO: 2607001, ใบส่งของชั่วคราว DO-2608-001 และใบแจ้งหนี้ INV-2608-001 รายการ Part Line ADC โครงการ PLC Control Board (Ethernet IP)</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>doc-pnp-do-2607001</v>
+        <v>doc-po-ptech-260901</v>
       </c>
       <c r="B24" t="str">
-        <v>DELIVERY_ORDER</v>
+        <v>PURCHASE_ORDER</v>
       </c>
       <c r="C24" t="str">
-        <v>DO-2608-001</v>
+        <v>PO-2609-001</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-08-20</v>
+        <v>2026-09-24</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-20</v>
+        <v>2026-10-24</v>
       </c>
       <c r="F24" t="str">
-        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+        <v>บริษัท ออมรอน อีเลคทรอนิกส์ (ประเทศไทย) จำกัด</v>
       </c>
       <c r="G24" t="str">
-        <v>2607001</v>
+        <v/>
       </c>
       <c r="H24" t="str">
-        <v>รายการ Part ที่จะจัดส่งของ Line ADC โครงการ PLC Control Board (Ethernet IP)</v>
+        <v/>
       </c>
       <c r="I24">
-        <v>1196840</v>
+        <v>9000</v>
       </c>
       <c r="J24">
-        <v>83778.8</v>
+        <v>630</v>
       </c>
       <c r="K24">
-        <v>1280618.8</v>
+        <v>9630</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>1280618.8</v>
+        <v>9630</v>
       </c>
       <c r="N24" t="str">
         <v>APPROVED</v>
       </c>
       <c r="O24" t="str">
-        <v>ใบส่งของชั่วคราว / ใบส่งสินค้า ตามใบสั่งซื้อ PO: 2607001 รายการ Part ที่จัดส่งของ Line ADC โครงการ PLC Control Board (Ethernet IP) เพื่อตรวจรับหน้างานโรงงานชลบุรี</v>
+        <v>จัดส่งที่: บริษัท วอร์สเกต จำกัด (สำนักงานใหญ่) หมู่บ้าน พฤกษาวิลล์ 46/1 เลขที่ 50/8 หมู่ 4 ตำบลคลองสาม อำเภอคลองหลวง จังหวัดปทุมธานี 12120 โทร. 083-066-7309</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>doc-pnp-inv-2607001</v>
+        <v>doc-pnp-qt-2609001</v>
       </c>
       <c r="B25" t="str">
-        <v>INVOICE</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C25" t="str">
-        <v>INV-2608-001</v>
+        <v>QT-2609-001</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-08-20</v>
+        <v>2026-09-24</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-09-19</v>
+        <v>2026-10-24</v>
       </c>
       <c r="F25" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="G25" t="str">
-        <v>2607001</v>
+        <v/>
       </c>
       <c r="H25" t="str">
-        <v>รายการ Part ที่จะจัดส่งของ Line ADC โครงการ PLC Control Board (Ethernet IP)</v>
+        <v>โครงการ Service Repair &amp; Maintenance OR Board (New Box OR)</v>
       </c>
       <c r="I25">
-        <v>1196840</v>
+        <v>569000</v>
       </c>
       <c r="J25">
-        <v>83778.8</v>
+        <v>39830</v>
       </c>
       <c r="K25">
-        <v>1280618.8</v>
+        <v>608830</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>1280618.8</v>
+        <v>608830</v>
       </c>
       <c r="N25" t="str">
-        <v>PENDING</v>
+        <v>APPROVED</v>
       </c>
       <c r="O25" t="str">
-        <v>ใบแจ้งหนี้ / ใบวางบิล ตามใบสั่งซื้อ PO: 2607001 และใบส่งของชั่วคราว DO-2608-001 (เงื่อนไขการชำระเงิน: เครดิต 30 วัน ครบกำหนด 19 ก.ย. 2569 โอนเข้าบัญชี KBANK บจก. วอร์สเกต)</v>
+        <v>เสนอราคาโครงการ Service Repair &amp; Maintenance OR Board (New Box OR) | ยืนยันราคาภายใน 30 วัน | เงื่อนไขการชำระเงิน: เครดิต 30 วัน</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>doc-pnp-tax-2607001</v>
+        <v>doc-pnp-qt-2609002</v>
       </c>
       <c r="B26" t="str">
-        <v>TAX_INVOICE</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C26" t="str">
-        <v>TAX-2608-001</v>
+        <v>QT-2609-003</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-08-20</v>
+        <v>2026-09-24</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-09-19</v>
+        <v>2026-10-24</v>
       </c>
       <c r="F26" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="G26" t="str">
-        <v>2607001</v>
+        <v>2609002</v>
       </c>
       <c r="H26" t="str">
-        <v>รายการ Part ที่จะจัดส่งของ Line ADC โครงการ PLC Control Board (Ethernet IP)</v>
+        <v/>
       </c>
       <c r="I26">
-        <v>1196840</v>
+        <v>148450</v>
       </c>
       <c r="J26">
-        <v>83778.8</v>
+        <v>10391.5</v>
       </c>
       <c r="K26">
-        <v>1280618.8</v>
+        <v>158841.5</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="M26">
-        <v>1280618.8</v>
+        <v>157491.5</v>
       </c>
       <c r="N26" t="str">
         <v>APPROVED</v>
       </c>
       <c r="O26" t="str">
-        <v>ใบกำกับภาษี ตามใบสั่งซื้อ PO: 2607001, ใบส่งของชั่วคราว DO-2608-001 และใบแจ้งหนี้ INV-2608-001 รายการ Part Line ADC โครงการ PLC Control Board (Ethernet IP)</v>
+        <v>โครงการจัดซื้ออุปกรณ์และติดตั้งเครือข่าย ตามใบสั่งซื้อลูกค้า PO: 2609002 ลงวันที่ 24 ก.ย. 2569 บจก. พีเอ็นพี เทคโนโลยี เกรท (เงื่อนไขการชำระเงิน: ชำระเมื่อส่งของครบตามใบสั่งซื้อ, วางบิลวันที่ 1-25 ของทุกเดือน, ใบกำกับภาษี + สำเนา 5 ใบ)</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>doc-po-ptech-260901</v>
+        <v>doc-kuroda-qt-dashboard-01</v>
       </c>
       <c r="B27" t="str">
-        <v>PURCHASE_ORDER</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C27" t="str">
-        <v>PO-2609-001</v>
+        <v>QT-2609-004</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="F27" t="str">
-        <v>บริษัท ออมรอน อีเลคทรอนิกส์ (ประเทศไทย) จำกัด</v>
+        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -4707,272 +4707,84 @@
         <v/>
       </c>
       <c r="I27">
-        <v>9000</v>
+        <v>47190</v>
       </c>
       <c r="J27">
-        <v>630</v>
+        <v>3303.3</v>
       </c>
       <c r="K27">
-        <v>9630</v>
+        <v>50493.3</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>9630</v>
+        <v>50493.3</v>
       </c>
       <c r="N27" t="str">
         <v>APPROVED</v>
       </c>
       <c r="O27" t="str">
-        <v>จัดส่งที่: บริษัท วอร์สเกต จำกัด (สำนักงานใหญ่) หมู่บ้าน พฤกษาวิลล์ 46/1 เลขที่ 50/8 หมู่ 4 ตำบลคลองสาม อำเภอคลองหลวง จังหวัดปทุมธานี 12120 โทร. 083-066-7309</v>
+        <v>เสนอราคาโครงการงาน Dashboard Data Monitor | เสนอ คุณนพพล อุ่นม่อน (Senior Specialist) บจก. คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) | กำหนดยืนราคา 30 วัน | เงื่อนไขการชำระเงิน: รายการนี้ส่งของครบ จ่าย 100%</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>doc-pnp-qt-2609001</v>
+        <v>doc-kuroda-qt-dashboard-02</v>
       </c>
       <c r="B28" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C28" t="str">
-        <v>QT-2609-001</v>
+        <v>QT-2609-005</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
       <c r="F28" t="str">
-        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>โครงการ Service Repair &amp; Maintenance OR Board (New Box OR)</v>
+        <v/>
       </c>
       <c r="I28">
-        <v>569000</v>
+        <v>150000</v>
       </c>
       <c r="J28">
-        <v>39830</v>
+        <v>10500</v>
       </c>
       <c r="K28">
-        <v>608830</v>
+        <v>160500</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="M28">
-        <v>608830</v>
+        <v>156000</v>
       </c>
       <c r="N28" t="str">
         <v>APPROVED</v>
       </c>
       <c r="O28" t="str">
-        <v>เสนอราคาโครงการ Service Repair &amp; Maintenance OR Board (New Box OR) | ยืนยันราคาภายใน 30 วัน | เงื่อนไขการชำระเงิน: เครดิต 30 วัน</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>doc-kuroda-qt-2609002</v>
-      </c>
-      <c r="B29" t="str">
-        <v>QUOTATION</v>
-      </c>
-      <c r="C29" t="str">
-        <v>QT-2609-002</v>
-      </c>
-      <c r="D29" t="str">
-        <v>2026-09-24</v>
-      </c>
-      <c r="E29" t="str">
-        <v>2026-10-24</v>
-      </c>
-      <c r="F29" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
-      </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
-      <c r="H29" t="str">
-        <v>โครงการ Smart Camera Pick &amp; Place / MVC with Camera 12 MP Inspection Parts</v>
-      </c>
-      <c r="I29">
-        <v>1004354</v>
-      </c>
-      <c r="J29">
-        <v>70304.78</v>
-      </c>
-      <c r="K29">
-        <v>1074658.78</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>1074658.78</v>
-      </c>
-      <c r="N29" t="str">
-        <v>APPROVED</v>
-      </c>
-      <c r="O29" t="str">
-        <v>เสนอราคาโครงการ Smart Camera Pick &amp; Place / MVC with Camera 12 MP Inspection Parts (Wenglor) | ยืนยันราคาภายใน 30 วัน | เงื่อนไขการชำระเงิน: รายการนี้ส่งของครบ จ่าย 100% | กำหนดส่งมอบ: DDP โรงงานลูกค้า | Remark : ไม่มี Computer</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>doc-pnp-qt-2609002</v>
-      </c>
-      <c r="B30" t="str">
-        <v>QUOTATION</v>
-      </c>
-      <c r="C30" t="str">
-        <v>QT-2609-003</v>
-      </c>
-      <c r="D30" t="str">
-        <v>2026-09-24</v>
-      </c>
-      <c r="E30" t="str">
-        <v>2026-10-24</v>
-      </c>
-      <c r="F30" t="str">
-        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
-      </c>
-      <c r="G30" t="str">
-        <v>2609002</v>
-      </c>
-      <c r="H30" t="str">
-        <v/>
-      </c>
-      <c r="I30">
-        <v>148450</v>
-      </c>
-      <c r="J30">
-        <v>10391.5</v>
-      </c>
-      <c r="K30">
-        <v>158841.5</v>
-      </c>
-      <c r="L30">
-        <v>1350</v>
-      </c>
-      <c r="M30">
-        <v>157491.5</v>
-      </c>
-      <c r="N30" t="str">
-        <v>APPROVED</v>
-      </c>
-      <c r="O30" t="str">
-        <v>โครงการจัดซื้ออุปกรณ์และติดตั้งเครือข่าย ตามใบสั่งซื้อลูกค้า PO: 2609002 ลงวันที่ 24 ก.ย. 2569 บจก. พีเอ็นพี เทคโนโลยี เกรท (เงื่อนไขการชำระเงิน: ชำระเมื่อส่งของครบตามใบสั่งซื้อ, วางบิลวันที่ 1-25 ของทุกเดือน, ใบกำกับภาษี + สำเนา 5 ใบ)</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>doc-kuroda-qt-dashboard-01</v>
-      </c>
-      <c r="B31" t="str">
-        <v>QUOTATION</v>
-      </c>
-      <c r="C31" t="str">
-        <v>QT-2609-004</v>
-      </c>
-      <c r="D31" t="str">
-        <v>2026-09-25</v>
-      </c>
-      <c r="E31" t="str">
-        <v>2026-10-25</v>
-      </c>
-      <c r="F31" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
-      </c>
-      <c r="G31" t="str">
-        <v/>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31">
-        <v>47190</v>
-      </c>
-      <c r="J31">
-        <v>3303.3</v>
-      </c>
-      <c r="K31">
-        <v>50493.3</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>50493.3</v>
-      </c>
-      <c r="N31" t="str">
-        <v>APPROVED</v>
-      </c>
-      <c r="O31" t="str">
-        <v>เสนอราคาโครงการงาน Dashboard Data Monitor | เสนอ คุณนพพล อุ่นม่อน (Senior Specialist) บจก. คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) | กำหนดยืนราคา 30 วัน | เงื่อนไขการชำระเงิน: รายการนี้ส่งของครบ จ่าย 100%</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>doc-kuroda-qt-dashboard-02</v>
-      </c>
-      <c r="B32" t="str">
-        <v>QUOTATION</v>
-      </c>
-      <c r="C32" t="str">
-        <v>QT-2609-005</v>
-      </c>
-      <c r="D32" t="str">
-        <v>2026-09-25</v>
-      </c>
-      <c r="E32" t="str">
-        <v>2026-10-25</v>
-      </c>
-      <c r="F32" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
-      </c>
-      <c r="G32" t="str">
-        <v/>
-      </c>
-      <c r="H32" t="str">
-        <v/>
-      </c>
-      <c r="I32">
-        <v>150000</v>
-      </c>
-      <c r="J32">
-        <v>10500</v>
-      </c>
-      <c r="K32">
-        <v>160500</v>
-      </c>
-      <c r="L32">
-        <v>4500</v>
-      </c>
-      <c r="M32">
-        <v>156000</v>
-      </c>
-      <c r="N32" t="str">
-        <v>APPROVED</v>
-      </c>
-      <c r="O32" t="str">
         <v>โครงการ: โปรแกรม ระบบ Dashboard Data Monitor | เสนอ คุณนพพล อุ่นม่อน (Senior Specialist) บจก. คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) | กำหนดยืนราคา 30 วัน | เงื่อนไขการชำระเงิน: รายการนี้มัดจำ 50% ก่อนเริ่มงาน | หักภาษี ณ ที่จ่าย 3%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O28"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L112"/>
+  <dimension ref="A1:L106"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5973,7 +5785,7 @@
         <v>2026-01-07</v>
       </c>
       <c r="D27" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -6011,7 +5823,7 @@
         <v>2026-01-07</v>
       </c>
       <c r="D28" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -6049,7 +5861,7 @@
         <v>2026-01-07</v>
       </c>
       <c r="D29" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -6087,7 +5899,7 @@
         <v>2026-01-07</v>
       </c>
       <c r="D30" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="E30">
         <v>4</v>
@@ -6125,7 +5937,7 @@
         <v>2026-01-07</v>
       </c>
       <c r="D31" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="E31">
         <v>5</v>
@@ -6163,7 +5975,7 @@
         <v>2026-01-07</v>
       </c>
       <c r="D32" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -6201,7 +6013,7 @@
         <v>2026-01-07</v>
       </c>
       <c r="D33" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="E33">
         <v>7</v>
@@ -6458,13 +6270,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INV-202607-001</v>
+        <v>QT-2512-2155</v>
       </c>
       <c r="B40" t="str">
-        <v>INVOICE</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C40" t="str">
-        <v>2026-07-15</v>
+        <v>2025-12-24</v>
       </c>
       <c r="D40" t="str">
         <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
@@ -6473,36 +6285,36 @@
         <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>PLC-S7-1200</v>
+        <v>TSF-ST-001</v>
       </c>
       <c r="G40" t="str">
-        <v>Siemens PLC SIMATIC S7-1200 CPU 1214C DC/DC/DC</v>
+        <v>Station Stacker Foam</v>
       </c>
       <c r="H40">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I40" t="str">
-        <v>เครื่อง</v>
+        <v>SET</v>
       </c>
       <c r="J40">
-        <v>18500</v>
+        <v>765394</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>92500</v>
+        <v>765394</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INV-202607-001</v>
+        <v>QT-2512-2155</v>
       </c>
       <c r="B41" t="str">
-        <v>INVOICE</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C41" t="str">
-        <v>2026-07-15</v>
+        <v>2025-12-24</v>
       </c>
       <c r="D41" t="str">
         <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
@@ -6511,139 +6323,139 @@
         <v>2</v>
       </c>
       <c r="F41" t="str">
-        <v>ENG-PROGRAMMING</v>
+        <v>TSF-ST-002</v>
       </c>
       <c r="G41" t="str">
-        <v>ค่าบริการเขียนโปรแกรม PLC / SCADA &amp; HMI Design</v>
+        <v>Station Open Bag &amp; Insert Foam</v>
       </c>
       <c r="H41">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I41" t="str">
-        <v>Man-Day</v>
+        <v>SET</v>
       </c>
       <c r="J41">
-        <v>15000</v>
+        <v>650215</v>
       </c>
       <c r="K41">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="L41">
-        <v>145000</v>
+        <v>650215</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>QT-202607-002</v>
+        <v>QT-2512-2155</v>
       </c>
       <c r="B42" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C42" t="str">
-        <v>2026-07-28</v>
+        <v>2025-12-24</v>
       </c>
       <c r="D42" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" t="str">
-        <v>SERVO-750W</v>
+        <v>TSF-ST-003</v>
       </c>
       <c r="G42" t="str">
-        <v>Omron Servo Motor &amp; Driver Set 750W 3000RPM</v>
+        <v>Station Pallet Stacker Foam</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I42" t="str">
-        <v>ชุด</v>
+        <v>SET</v>
       </c>
       <c r="J42">
-        <v>24500</v>
+        <v>690391</v>
       </c>
       <c r="K42">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="L42">
-        <v>96000</v>
+        <v>690391</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>QT-202607-002</v>
+        <v>QT-2512-2155</v>
       </c>
       <c r="B43" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C43" t="str">
-        <v>2026-07-28</v>
+        <v>2025-12-24</v>
       </c>
       <c r="D43" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F43" t="str">
-        <v>ENG-COMMISSION</v>
+        <v>TSF-ST-004</v>
       </c>
       <c r="G43" t="str">
-        <v>ค่าบริการทดสอบและติดตั้งระบบหน้างาน (On-site Commissioning)</v>
+        <v>Contron Box System</v>
       </c>
       <c r="H43">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I43" t="str">
-        <v>Man-Day</v>
+        <v>SET</v>
       </c>
       <c r="J43">
-        <v>12000</v>
+        <v>312000</v>
       </c>
       <c r="K43">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>60000</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>PO-202607-001</v>
+        <v>QT-2512-2155</v>
       </c>
       <c r="B44" t="str">
-        <v>PURCHASE_ORDER</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C44" t="str">
-        <v>2026-07-20</v>
+        <v>2025-12-24</v>
       </c>
       <c r="D44" t="str">
         <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F44" t="str">
-        <v>PLC-S7-1200</v>
+        <v>TSF-SRV-001</v>
       </c>
       <c r="G44" t="str">
-        <v>Siemens PLC SIMATIC S7-1200 CPU 1214C</v>
+        <v>Manpower and labor cost</v>
       </c>
       <c r="H44">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I44" t="str">
-        <v>เครื่อง</v>
+        <v>JOB</v>
       </c>
       <c r="J44">
-        <v>13200</v>
+        <v>575000</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>132000</v>
+        <v>575000</v>
       </c>
     </row>
     <row r="45">
@@ -6657,31 +6469,31 @@
         <v>2025-12-24</v>
       </c>
       <c r="D45" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F45" t="str">
-        <v>TSF-ST-001</v>
+        <v>TSF-SRV-002</v>
       </c>
       <c r="G45" t="str">
-        <v>Station Stacker Foam</v>
+        <v>Transportation and accommodation</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45" t="str">
-        <v>SET</v>
+        <v>JOB</v>
       </c>
       <c r="J45">
-        <v>765394</v>
+        <v>45000</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>765394</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="46">
@@ -6695,232 +6507,232 @@
         <v>2025-12-24</v>
       </c>
       <c r="D46" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F46" t="str">
-        <v>TSF-ST-002</v>
+        <v>TSF-SRV-003</v>
       </c>
       <c r="G46" t="str">
-        <v>Station Open Bag &amp; Insert Foam</v>
+        <v>Profit / Project Management &amp; Warranty 1 year</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46" t="str">
-        <v>SET</v>
+        <v>JOB</v>
       </c>
       <c r="J46">
-        <v>650215</v>
+        <v>607600</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>650215</v>
+        <v>607600</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>QT-2512-2155</v>
+        <v>QT-2505-004</v>
       </c>
       <c r="B47" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C47" t="str">
-        <v>2025-12-24</v>
+        <v>2025-05-07</v>
       </c>
       <c r="D47" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>TSF-ST-003</v>
+        <v>SW-TRACE-CORR</v>
       </c>
       <c r="G47" t="str">
-        <v>Station Pallet Stacker Foam</v>
+        <v>Traceability Corrugating Line</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" t="str">
-        <v>SET</v>
+        <v>Job</v>
       </c>
       <c r="J47">
-        <v>690391</v>
+        <v>1005002.64</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>690391</v>
+        <v>1005002.64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>QT-2512-2155</v>
+        <v>QT-2505-004</v>
       </c>
       <c r="B48" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C48" t="str">
-        <v>2025-12-24</v>
+        <v>2025-05-07</v>
       </c>
       <c r="D48" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>TSF-ST-004</v>
+        <v>SW-TRACE-WIND</v>
       </c>
       <c r="G48" t="str">
-        <v>Contron Box System</v>
+        <v>Traceability Winding Line</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48" t="str">
-        <v>SET</v>
+        <v>Job</v>
       </c>
       <c r="J48">
-        <v>312000</v>
+        <v>707304.38</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>312000</v>
+        <v>707304.38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>QT-2512-2155</v>
+        <v>QT-2505-004</v>
       </c>
       <c r="B49" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C49" t="str">
-        <v>2025-12-24</v>
+        <v>2025-05-07</v>
       </c>
       <c r="D49" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F49" t="str">
-        <v>TSF-SRV-001</v>
+        <v>SW-TRACE-ADH</v>
       </c>
       <c r="G49" t="str">
-        <v>Manpower and labor cost</v>
+        <v>Traceability Adhesive &amp; Spin Winding Line</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49" t="str">
-        <v>JOB</v>
+        <v>Job</v>
       </c>
       <c r="J49">
-        <v>575000</v>
+        <v>874426.94</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>575000</v>
+        <v>874426.94</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>QT-2512-2155</v>
+        <v>QT-2505-004</v>
       </c>
       <c r="B50" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C50" t="str">
-        <v>2025-12-24</v>
+        <v>2025-05-07</v>
       </c>
       <c r="D50" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F50" t="str">
-        <v>TSF-SRV-002</v>
+        <v>SW-TRACE-DF4</v>
       </c>
       <c r="G50" t="str">
-        <v>Transportation and accommodation</v>
+        <v>Traceability DF4 Line</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50" t="str">
-        <v>JOB</v>
+        <v>Job</v>
       </c>
       <c r="J50">
-        <v>45000</v>
+        <v>1203060.14</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>45000</v>
+        <v>1203060.14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>QT-2512-2155</v>
+        <v>QT-2505-004</v>
       </c>
       <c r="B51" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C51" t="str">
-        <v>2025-12-24</v>
+        <v>2025-05-07</v>
       </c>
       <c r="D51" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F51" t="str">
-        <v>TSF-SRV-003</v>
+        <v>SW-TRACE-PACK</v>
       </c>
       <c r="G51" t="str">
-        <v>Profit / Project Management &amp; Warranty 1 year</v>
+        <v>Traceability Packing Line</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" t="str">
-        <v>JOB</v>
+        <v>Job</v>
       </c>
       <c r="J51">
-        <v>607600</v>
+        <v>553196.28</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>607600</v>
+        <v>553196.28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>QT-2505-004</v>
+        <v>QT-2605-001</v>
       </c>
       <c r="B52" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C52" t="str">
-        <v>2025-05-07</v>
+        <v>2026-05-02</v>
       </c>
       <c r="D52" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
@@ -6929,36 +6741,36 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>SW-TRACE-CORR</v>
+        <v>PNP-FAB-001</v>
       </c>
       <c r="G52" t="str">
-        <v>Traceability Corrugating Line</v>
+        <v>Standard and Feb Part</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52" t="str">
-        <v>Job</v>
+        <v>Set</v>
       </c>
       <c r="J52">
-        <v>1005002.64</v>
+        <v>1140000</v>
       </c>
       <c r="K52">
         <v>0</v>
       </c>
       <c r="L52">
-        <v>1005002.64</v>
+        <v>1140000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>QT-2505-004</v>
+        <v>QT-2605-001</v>
       </c>
       <c r="B53" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C53" t="str">
-        <v>2025-05-07</v>
+        <v>2026-05-02</v>
       </c>
       <c r="D53" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
@@ -6967,10 +6779,10 @@
         <v>2</v>
       </c>
       <c r="F53" t="str">
-        <v>SW-TRACE-WIND</v>
+        <v>PNP-LAB-001</v>
       </c>
       <c r="G53" t="str">
-        <v>Traceability Winding Line</v>
+        <v>Manpower and Labor Cost</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -6979,24 +6791,24 @@
         <v>Job</v>
       </c>
       <c r="J53">
-        <v>707304.38</v>
+        <v>670000</v>
       </c>
       <c r="K53">
         <v>0</v>
       </c>
       <c r="L53">
-        <v>707304.38</v>
+        <v>670000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>QT-2505-004</v>
+        <v>QT-2605-001</v>
       </c>
       <c r="B54" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C54" t="str">
-        <v>2025-05-07</v>
+        <v>2026-05-02</v>
       </c>
       <c r="D54" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
@@ -7005,36 +6817,36 @@
         <v>3</v>
       </c>
       <c r="F54" t="str">
-        <v>SW-TRACE-ADH</v>
+        <v>PNP-LOG-001</v>
       </c>
       <c r="G54" t="str">
-        <v>Traceability Adhesive &amp; Spin Winding Line</v>
+        <v>Transportation and accommodation</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54" t="str">
-        <v>Job</v>
+        <v>EA</v>
       </c>
       <c r="J54">
-        <v>874426.94</v>
+        <v>45000</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>874426.94</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>QT-2505-004</v>
+        <v>QT-2605-001</v>
       </c>
       <c r="B55" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C55" t="str">
-        <v>2025-05-07</v>
+        <v>2026-05-02</v>
       </c>
       <c r="D55" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
@@ -7043,68 +6855,68 @@
         <v>4</v>
       </c>
       <c r="F55" t="str">
-        <v>SW-TRACE-DF4</v>
+        <v>PNP-PM-001</v>
       </c>
       <c r="G55" t="str">
-        <v>Traceability DF4 Line</v>
+        <v>Project Management</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55" t="str">
-        <v>Job</v>
+        <v>EA</v>
       </c>
       <c r="J55">
-        <v>1203060.14</v>
+        <v>556500</v>
       </c>
       <c r="K55">
         <v>0</v>
       </c>
       <c r="L55">
-        <v>1203060.14</v>
+        <v>556500</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>QT-2505-004</v>
+        <v>QT-2605-002</v>
       </c>
       <c r="B56" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C56" t="str">
-        <v>2025-05-07</v>
+        <v>2026-05-02</v>
       </c>
       <c r="D56" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>SW-TRACE-PACK</v>
+        <v>PNP-FAB-002</v>
       </c>
       <c r="G56" t="str">
-        <v>Traceability Packing Line</v>
+        <v>Standard and Feb Part</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56" t="str">
-        <v>Job</v>
+        <v>Set</v>
       </c>
       <c r="J56">
-        <v>553196.28</v>
+        <v>641000</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>553196.28</v>
+        <v>641000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>QT-2605-001</v>
+        <v>QT-2605-002</v>
       </c>
       <c r="B57" t="str">
         <v>QUOTATION</v>
@@ -7116,33 +6928,33 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="str">
-        <v>PNP-FAB-001</v>
+        <v>PNP-LAB-002</v>
       </c>
       <c r="G57" t="str">
-        <v>Standard and Feb Part</v>
+        <v>Manpower and Labor Cost</v>
       </c>
       <c r="H57">
         <v>1</v>
       </c>
       <c r="I57" t="str">
-        <v>Set</v>
+        <v>Job</v>
       </c>
       <c r="J57">
-        <v>1140000</v>
+        <v>220000</v>
       </c>
       <c r="K57">
         <v>0</v>
       </c>
       <c r="L57">
-        <v>1140000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>QT-2605-001</v>
+        <v>QT-2605-002</v>
       </c>
       <c r="B58" t="str">
         <v>QUOTATION</v>
@@ -7154,33 +6966,33 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" t="str">
-        <v>PNP-LAB-001</v>
+        <v>PNP-LOG-002</v>
       </c>
       <c r="G58" t="str">
-        <v>Manpower and Labor Cost</v>
+        <v>Transportation and accommodation</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58" t="str">
-        <v>Job</v>
+        <v>EA</v>
       </c>
       <c r="J58">
-        <v>670000</v>
+        <v>45000</v>
       </c>
       <c r="K58">
         <v>0</v>
       </c>
       <c r="L58">
-        <v>670000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>QT-2605-001</v>
+        <v>QT-2605-002</v>
       </c>
       <c r="B59" t="str">
         <v>QUOTATION</v>
@@ -7192,13 +7004,13 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" t="str">
-        <v>PNP-LOG-001</v>
+        <v>PNP-PM-002</v>
       </c>
       <c r="G59" t="str">
-        <v>Transportation and accommodation</v>
+        <v>Project Management</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -7207,62 +7019,62 @@
         <v>EA</v>
       </c>
       <c r="J59">
-        <v>45000</v>
+        <v>271800</v>
       </c>
       <c r="K59">
         <v>0</v>
       </c>
       <c r="L59">
-        <v>45000</v>
+        <v>271800</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>QT-2605-001</v>
+        <v>REC-2605-002/1</v>
       </c>
       <c r="B60" t="str">
-        <v>QUOTATION</v>
+        <v>RECEIPT</v>
       </c>
       <c r="C60" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-25</v>
       </c>
       <c r="D60" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E60">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>PNP-PM-001</v>
+        <v>PNP-DP30-Z7</v>
       </c>
       <c r="G60" t="str">
-        <v>Project Management</v>
+        <v>รับชำระเงินงวดที่ 1 : ค่ามัดจำเริ่มต้นโครงการ 30% (Downpayment 30%)</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60" t="str">
-        <v>EA</v>
+        <v>งวด</v>
       </c>
       <c r="J60">
-        <v>556500</v>
+        <v>353340</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>556500</v>
+        <v>353340</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>QT-2605-002</v>
+        <v>QT-2607-001</v>
       </c>
       <c r="B61" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C61" t="str">
-        <v>2026-05-02</v>
+        <v>2026-07-17</v>
       </c>
       <c r="D61" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
@@ -7271,36 +7083,36 @@
         <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>PNP-FAB-002</v>
+        <v>PLC-ETH-001</v>
       </c>
       <c r="G61" t="str">
-        <v>Standard and Feb Part</v>
+        <v>PLC Control Board (Ethernet IP)</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I61" t="str">
-        <v>Set</v>
+        <v>EA</v>
       </c>
       <c r="J61">
-        <v>641000</v>
+        <v>35040</v>
       </c>
       <c r="K61">
         <v>0</v>
       </c>
       <c r="L61">
-        <v>641000</v>
+        <v>735840</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>QT-2605-002</v>
+        <v>QT-2607-001</v>
       </c>
       <c r="B62" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C62" t="str">
-        <v>2026-05-02</v>
+        <v>2026-07-17</v>
       </c>
       <c r="D62" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
@@ -7309,36 +7121,36 @@
         <v>2</v>
       </c>
       <c r="F62" t="str">
-        <v>PNP-LAB-002</v>
+        <v>PLC-SUB-001</v>
       </c>
       <c r="G62" t="str">
-        <v>Manpower and Labor Cost</v>
+        <v>Sub PLC Box + Aceessories</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I62" t="str">
-        <v>Job</v>
+        <v>EA</v>
       </c>
       <c r="J62">
-        <v>220000</v>
+        <v>26000</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62">
-        <v>220000</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>QT-2605-002</v>
+        <v>QT-2607-001</v>
       </c>
       <c r="B63" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C63" t="str">
-        <v>2026-05-02</v>
+        <v>2026-07-17</v>
       </c>
       <c r="D63" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
@@ -7347,10 +7159,10 @@
         <v>3</v>
       </c>
       <c r="F63" t="str">
-        <v>PNP-LOG-002</v>
+        <v>PC-RACK-001</v>
       </c>
       <c r="G63" t="str">
-        <v>Transportation and accommodation</v>
+        <v>Rack PC Center</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -7359,24 +7171,24 @@
         <v>EA</v>
       </c>
       <c r="J63">
-        <v>45000</v>
+        <v>12000</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>45000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>QT-2605-002</v>
+        <v>QT-2607-001</v>
       </c>
       <c r="B64" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C64" t="str">
-        <v>2026-05-02</v>
+        <v>2026-07-17</v>
       </c>
       <c r="D64" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
@@ -7385,10 +7197,10 @@
         <v>4</v>
       </c>
       <c r="F64" t="str">
-        <v>PNP-PM-002</v>
+        <v>PLC-DC-001</v>
       </c>
       <c r="G64" t="str">
-        <v>Project Management</v>
+        <v>PLC Data Center Line</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -7397,51 +7209,51 @@
         <v>EA</v>
       </c>
       <c r="J64">
-        <v>271800</v>
+        <v>150000</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>271800</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>REC-2605-002/1</v>
+        <v>QT-2607-001</v>
       </c>
       <c r="B65" t="str">
-        <v>RECEIPT</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C65" t="str">
-        <v>2026-05-25</v>
+        <v>2026-07-17</v>
       </c>
       <c r="D65" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F65" t="str">
-        <v>PNP-DP30-Z7</v>
+        <v>STR-SUP-001</v>
       </c>
       <c r="G65" t="str">
-        <v>รับชำระเงินงวดที่ 1 : ค่ามัดจำเริ่มต้นโครงการ 30% (Downpayment 30%)</v>
+        <v>Stucture Support</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65" t="str">
-        <v>งวด</v>
+        <v>EA</v>
       </c>
       <c r="J65">
-        <v>353340</v>
+        <v>20000</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>353340</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="66">
@@ -7458,28 +7270,28 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F66" t="str">
-        <v>PLC-ETH-001</v>
+        <v>PC-CTR-001</v>
       </c>
       <c r="G66" t="str">
-        <v>PLC Control Board (Ethernet IP)</v>
+        <v>PC Center</v>
       </c>
       <c r="H66">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I66" t="str">
         <v>EA</v>
       </c>
       <c r="J66">
-        <v>35040</v>
+        <v>123000</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>735840</v>
+        <v>123000</v>
       </c>
     </row>
     <row r="67">
@@ -7496,28 +7308,28 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F67" t="str">
-        <v>PLC-SUB-001</v>
+        <v>PNP-LAB-001</v>
       </c>
       <c r="G67" t="str">
-        <v>Sub PLC Box + Aceessories</v>
+        <v>Manpower and Labor Cost</v>
       </c>
       <c r="H67">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I67" t="str">
-        <v>EA</v>
+        <v>Job</v>
       </c>
       <c r="J67">
-        <v>26000</v>
+        <v>670000</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>156000</v>
+        <v>670000</v>
       </c>
     </row>
     <row r="68">
@@ -7534,13 +7346,13 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F68" t="str">
-        <v>PC-RACK-001</v>
+        <v>PNP-LOG-001</v>
       </c>
       <c r="G68" t="str">
-        <v>Rack PC Center</v>
+        <v>Transportation and accommodation</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -7549,13 +7361,13 @@
         <v>EA</v>
       </c>
       <c r="J68">
-        <v>12000</v>
+        <v>45000</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>12000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="69">
@@ -7572,13 +7384,13 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E69">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F69" t="str">
-        <v>PLC-DC-001</v>
+        <v>PNP-PM-2607</v>
       </c>
       <c r="G69" t="str">
-        <v>PLC Data Center Line</v>
+        <v>Project Management</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -7587,203 +7399,203 @@
         <v>EA</v>
       </c>
       <c r="J69">
-        <v>150000</v>
+        <v>573552</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>150000</v>
+        <v>573552</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>QT-2607-001</v>
+        <v>DO-2608-001</v>
       </c>
       <c r="B70" t="str">
-        <v>QUOTATION</v>
+        <v>DELIVERY_ORDER</v>
       </c>
       <c r="C70" t="str">
-        <v>2026-07-17</v>
+        <v>2026-08-20</v>
       </c>
       <c r="D70" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E70">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F70" t="str">
-        <v>STR-SUP-001</v>
+        <v>CJ1W-EIP21</v>
       </c>
       <c r="G70" t="str">
-        <v>Stucture Support</v>
+        <v>1.1 PLC Control Board (Ethernet IP)</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I70" t="str">
         <v>EA</v>
       </c>
       <c r="J70">
-        <v>20000</v>
+        <v>35040</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>20000</v>
+        <v>735840</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>QT-2607-001</v>
+        <v>DO-2608-001</v>
       </c>
       <c r="B71" t="str">
-        <v>QUOTATION</v>
+        <v>DELIVERY_ORDER</v>
       </c>
       <c r="C71" t="str">
-        <v>2026-07-17</v>
+        <v>2026-08-20</v>
       </c>
       <c r="D71" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E71">
+        <v>2</v>
+      </c>
+      <c r="F71" t="str">
+        <v>PLC-SUB-001</v>
+      </c>
+      <c r="G71" t="str">
+        <v>2. Sub PLC Box + Accessories 6 SET</v>
+      </c>
+      <c r="H71">
         <v>6</v>
       </c>
-      <c r="F71" t="str">
-        <v>PC-CTR-001</v>
-      </c>
-      <c r="G71" t="str">
-        <v>PC Center</v>
-      </c>
-      <c r="H71">
-        <v>1</v>
-      </c>
       <c r="I71" t="str">
-        <v>EA</v>
+        <v>SET</v>
       </c>
       <c r="J71">
-        <v>123000</v>
+        <v>26000</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71">
-        <v>123000</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>QT-2607-001</v>
+        <v>DO-2608-001</v>
       </c>
       <c r="B72" t="str">
-        <v>QUOTATION</v>
+        <v>DELIVERY_ORDER</v>
       </c>
       <c r="C72" t="str">
-        <v>2026-07-17</v>
+        <v>2026-08-20</v>
       </c>
       <c r="D72" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F72" t="str">
-        <v>PNP-LAB-001</v>
+        <v>PC-RACK-001</v>
       </c>
       <c r="G72" t="str">
-        <v>Manpower and Labor Cost</v>
+        <v>3. Rack PC Center</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72" t="str">
-        <v>Job</v>
+        <v>EA</v>
       </c>
       <c r="J72">
-        <v>670000</v>
+        <v>12000</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>670000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>QT-2607-001</v>
+        <v>DO-2608-001</v>
       </c>
       <c r="B73" t="str">
-        <v>QUOTATION</v>
+        <v>DELIVERY_ORDER</v>
       </c>
       <c r="C73" t="str">
-        <v>2026-07-17</v>
+        <v>2026-08-20</v>
       </c>
       <c r="D73" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E73">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F73" t="str">
-        <v>PNP-LOG-001</v>
+        <v>PLC-DC-001</v>
       </c>
       <c r="G73" t="str">
-        <v>Transportation and accommodation</v>
+        <v>4. PLC Data Center Line 1 SET</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73" t="str">
-        <v>EA</v>
+        <v>SET</v>
       </c>
       <c r="J73">
-        <v>45000</v>
+        <v>150000</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>45000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>QT-2607-001</v>
+        <v>DO-2608-001</v>
       </c>
       <c r="B74" t="str">
-        <v>QUOTATION</v>
+        <v>DELIVERY_ORDER</v>
       </c>
       <c r="C74" t="str">
-        <v>2026-07-17</v>
+        <v>2026-08-20</v>
       </c>
       <c r="D74" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E74">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F74" t="str">
-        <v>PNP-PM-2607</v>
+        <v>STR-SUP-001</v>
       </c>
       <c r="G74" t="str">
-        <v>Project Management</v>
+        <v>5. Structure Support</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74" t="str">
-        <v>EA</v>
+        <v>SET</v>
       </c>
       <c r="J74">
-        <v>573552</v>
+        <v>20000</v>
       </c>
       <c r="K74">
         <v>0</v>
       </c>
       <c r="L74">
-        <v>573552</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="75">
@@ -7800,36 +7612,36 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F75" t="str">
-        <v>CJ1W-EIP21</v>
+        <v>PC-CTR-001</v>
       </c>
       <c r="G75" t="str">
-        <v>1.1 PLC Control Board (Ethernet IP)</v>
+        <v>6. PC Center</v>
       </c>
       <c r="H75">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I75" t="str">
-        <v>EA</v>
+        <v>SET</v>
       </c>
       <c r="J75">
-        <v>35040</v>
+        <v>123000</v>
       </c>
       <c r="K75">
         <v>0</v>
       </c>
       <c r="L75">
-        <v>735840</v>
+        <v>123000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DO-2608-001</v>
+        <v>INV-2608-001</v>
       </c>
       <c r="B76" t="str">
-        <v>DELIVERY_ORDER</v>
+        <v>INVOICE</v>
       </c>
       <c r="C76" t="str">
         <v>2026-08-20</v>
@@ -7838,36 +7650,36 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" t="str">
-        <v>PLC-SUB-001</v>
+        <v>CJ1W-EIP21</v>
       </c>
       <c r="G76" t="str">
-        <v>2. Sub PLC Box + Accessories 6 SET</v>
+        <v>1.1 PLC Control Board (Ethernet IP)</v>
       </c>
       <c r="H76">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I76" t="str">
-        <v>SET</v>
+        <v>EA</v>
       </c>
       <c r="J76">
-        <v>26000</v>
+        <v>35040</v>
       </c>
       <c r="K76">
         <v>0</v>
       </c>
       <c r="L76">
-        <v>156000</v>
+        <v>735840</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>DO-2608-001</v>
+        <v>INV-2608-001</v>
       </c>
       <c r="B77" t="str">
-        <v>DELIVERY_ORDER</v>
+        <v>INVOICE</v>
       </c>
       <c r="C77" t="str">
         <v>2026-08-20</v>
@@ -7876,36 +7688,36 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" t="str">
-        <v>PC-RACK-001</v>
+        <v>PLC-SUB-001</v>
       </c>
       <c r="G77" t="str">
-        <v>3. Rack PC Center</v>
+        <v>2. Sub PLC Box + Accessories 6 SET</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I77" t="str">
-        <v>EA</v>
+        <v>SET</v>
       </c>
       <c r="J77">
-        <v>12000</v>
+        <v>26000</v>
       </c>
       <c r="K77">
         <v>0</v>
       </c>
       <c r="L77">
-        <v>12000</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>DO-2608-001</v>
+        <v>INV-2608-001</v>
       </c>
       <c r="B78" t="str">
-        <v>DELIVERY_ORDER</v>
+        <v>INVOICE</v>
       </c>
       <c r="C78" t="str">
         <v>2026-08-20</v>
@@ -7914,36 +7726,36 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F78" t="str">
-        <v>PLC-DC-001</v>
+        <v>PC-RACK-001</v>
       </c>
       <c r="G78" t="str">
-        <v>4. PLC Data Center Line 1 SET</v>
+        <v>3. Rack PC Center</v>
       </c>
       <c r="H78">
         <v>1</v>
       </c>
       <c r="I78" t="str">
-        <v>SET</v>
+        <v>EA</v>
       </c>
       <c r="J78">
-        <v>150000</v>
+        <v>12000</v>
       </c>
       <c r="K78">
         <v>0</v>
       </c>
       <c r="L78">
-        <v>150000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>DO-2608-001</v>
+        <v>INV-2608-001</v>
       </c>
       <c r="B79" t="str">
-        <v>DELIVERY_ORDER</v>
+        <v>INVOICE</v>
       </c>
       <c r="C79" t="str">
         <v>2026-08-20</v>
@@ -7952,13 +7764,13 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F79" t="str">
-        <v>STR-SUP-001</v>
+        <v>PLC-DC-001</v>
       </c>
       <c r="G79" t="str">
-        <v>5. Structure Support</v>
+        <v>4. PLC Data Center Line 1 SET</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -7967,21 +7779,21 @@
         <v>SET</v>
       </c>
       <c r="J79">
-        <v>20000</v>
+        <v>150000</v>
       </c>
       <c r="K79">
         <v>0</v>
       </c>
       <c r="L79">
-        <v>20000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>DO-2608-001</v>
+        <v>INV-2608-001</v>
       </c>
       <c r="B80" t="str">
-        <v>DELIVERY_ORDER</v>
+        <v>INVOICE</v>
       </c>
       <c r="C80" t="str">
         <v>2026-08-20</v>
@@ -7990,13 +7802,13 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F80" t="str">
-        <v>PC-CTR-001</v>
+        <v>STR-SUP-001</v>
       </c>
       <c r="G80" t="str">
-        <v>6. PC Center</v>
+        <v>5. Structure Support</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -8005,13 +7817,13 @@
         <v>SET</v>
       </c>
       <c r="J80">
-        <v>123000</v>
+        <v>20000</v>
       </c>
       <c r="K80">
         <v>0</v>
       </c>
       <c r="L80">
-        <v>123000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="81">
@@ -8028,36 +7840,36 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E81">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F81" t="str">
-        <v>CJ1W-EIP21</v>
+        <v>PC-CTR-001</v>
       </c>
       <c r="G81" t="str">
-        <v>1.1 PLC Control Board (Ethernet IP)</v>
+        <v>6. PC Center</v>
       </c>
       <c r="H81">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I81" t="str">
-        <v>EA</v>
+        <v>SET</v>
       </c>
       <c r="J81">
-        <v>35040</v>
+        <v>123000</v>
       </c>
       <c r="K81">
         <v>0</v>
       </c>
       <c r="L81">
-        <v>735840</v>
+        <v>123000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>INV-2608-001</v>
+        <v>TAX-2608-001</v>
       </c>
       <c r="B82" t="str">
-        <v>INVOICE</v>
+        <v>TAX_INVOICE</v>
       </c>
       <c r="C82" t="str">
         <v>2026-08-20</v>
@@ -8066,36 +7878,36 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" t="str">
-        <v>PLC-SUB-001</v>
+        <v>CJ1W-EIP21</v>
       </c>
       <c r="G82" t="str">
-        <v>2. Sub PLC Box + Accessories 6 SET</v>
+        <v>1.1 PLC Control Board (Ethernet IP)</v>
       </c>
       <c r="H82">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I82" t="str">
-        <v>SET</v>
+        <v>EA</v>
       </c>
       <c r="J82">
-        <v>26000</v>
+        <v>35040</v>
       </c>
       <c r="K82">
         <v>0</v>
       </c>
       <c r="L82">
-        <v>156000</v>
+        <v>735840</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>INV-2608-001</v>
+        <v>TAX-2608-001</v>
       </c>
       <c r="B83" t="str">
-        <v>INVOICE</v>
+        <v>TAX_INVOICE</v>
       </c>
       <c r="C83" t="str">
         <v>2026-08-20</v>
@@ -8104,36 +7916,36 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F83" t="str">
-        <v>PC-RACK-001</v>
+        <v>PLC-SUB-001</v>
       </c>
       <c r="G83" t="str">
-        <v>3. Rack PC Center</v>
+        <v>2. Sub PLC Box + Accessories 6 SET</v>
       </c>
       <c r="H83">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I83" t="str">
-        <v>EA</v>
+        <v>SET</v>
       </c>
       <c r="J83">
-        <v>12000</v>
+        <v>26000</v>
       </c>
       <c r="K83">
         <v>0</v>
       </c>
       <c r="L83">
-        <v>12000</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>INV-2608-001</v>
+        <v>TAX-2608-001</v>
       </c>
       <c r="B84" t="str">
-        <v>INVOICE</v>
+        <v>TAX_INVOICE</v>
       </c>
       <c r="C84" t="str">
         <v>2026-08-20</v>
@@ -8142,36 +7954,36 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F84" t="str">
-        <v>PLC-DC-001</v>
+        <v>PC-RACK-001</v>
       </c>
       <c r="G84" t="str">
-        <v>4. PLC Data Center Line 1 SET</v>
+        <v>3. Rack PC Center</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84" t="str">
-        <v>SET</v>
+        <v>EA</v>
       </c>
       <c r="J84">
-        <v>150000</v>
+        <v>12000</v>
       </c>
       <c r="K84">
         <v>0</v>
       </c>
       <c r="L84">
-        <v>150000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>INV-2608-001</v>
+        <v>TAX-2608-001</v>
       </c>
       <c r="B85" t="str">
-        <v>INVOICE</v>
+        <v>TAX_INVOICE</v>
       </c>
       <c r="C85" t="str">
         <v>2026-08-20</v>
@@ -8180,13 +7992,13 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F85" t="str">
-        <v>STR-SUP-001</v>
+        <v>PLC-DC-001</v>
       </c>
       <c r="G85" t="str">
-        <v>5. Structure Support</v>
+        <v>4. PLC Data Center Line 1 SET</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -8195,21 +8007,21 @@
         <v>SET</v>
       </c>
       <c r="J85">
-        <v>20000</v>
+        <v>150000</v>
       </c>
       <c r="K85">
         <v>0</v>
       </c>
       <c r="L85">
-        <v>20000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>INV-2608-001</v>
+        <v>TAX-2608-001</v>
       </c>
       <c r="B86" t="str">
-        <v>INVOICE</v>
+        <v>TAX_INVOICE</v>
       </c>
       <c r="C86" t="str">
         <v>2026-08-20</v>
@@ -8218,13 +8030,13 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F86" t="str">
-        <v>PC-CTR-001</v>
+        <v>STR-SUP-001</v>
       </c>
       <c r="G86" t="str">
-        <v>6. PC Center</v>
+        <v>5. Structure Support</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -8233,13 +8045,13 @@
         <v>SET</v>
       </c>
       <c r="J86">
-        <v>123000</v>
+        <v>20000</v>
       </c>
       <c r="K86">
         <v>0</v>
       </c>
       <c r="L86">
-        <v>123000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="87">
@@ -8256,299 +8068,299 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F87" t="str">
-        <v>CJ1W-EIP21</v>
+        <v>PC-CTR-001</v>
       </c>
       <c r="G87" t="str">
-        <v>1.1 PLC Control Board (Ethernet IP)</v>
+        <v>6. PC Center</v>
       </c>
       <c r="H87">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I87" t="str">
-        <v>EA</v>
+        <v>SET</v>
       </c>
       <c r="J87">
-        <v>35040</v>
+        <v>123000</v>
       </c>
       <c r="K87">
         <v>0</v>
       </c>
       <c r="L87">
-        <v>735840</v>
+        <v>123000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>TAX-2608-001</v>
+        <v>PO-2609-001</v>
       </c>
       <c r="B88" t="str">
-        <v>TAX_INVOICE</v>
+        <v>PURCHASE_ORDER</v>
       </c>
       <c r="C88" t="str">
-        <v>2026-08-20</v>
+        <v>2026-09-24</v>
       </c>
       <c r="D88" t="str">
-        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+        <v>บริษัท ออมรอน อีเลคทรอนิกส์ (ประเทศไทย) จำกัด</v>
       </c>
       <c r="E88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="str">
-        <v>PLC-SUB-001</v>
+        <v>SPINDLE-ROLL-01</v>
       </c>
       <c r="G88" t="str">
-        <v>2. Sub PLC Box + Accessories 6 SET</v>
+        <v>Roller Paper Printer Spindle (แกนหมุนกระดาษเครื่องพิมพ์อัปเกรด)</v>
       </c>
       <c r="H88">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I88" t="str">
-        <v>SET</v>
+        <v>Set</v>
       </c>
       <c r="J88">
-        <v>26000</v>
+        <v>300</v>
       </c>
       <c r="K88">
         <v>0</v>
       </c>
       <c r="L88">
-        <v>156000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>TAX-2608-001</v>
+        <v>PO-2609-001</v>
       </c>
       <c r="B89" t="str">
-        <v>TAX_INVOICE</v>
+        <v>PURCHASE_ORDER</v>
       </c>
       <c r="C89" t="str">
-        <v>2026-08-20</v>
+        <v>2026-09-24</v>
       </c>
       <c r="D89" t="str">
-        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+        <v>บริษัท ออมรอน อีเลคทรอนิกส์ (ประเทศไทย) จำกัด</v>
       </c>
       <c r="E89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F89" t="str">
-        <v>PC-RACK-001</v>
+        <v>BOX-MINI-JB01</v>
       </c>
       <c r="G89" t="str">
-        <v>3. Rack PC Center</v>
+        <v>mini junction box</v>
       </c>
       <c r="H89">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I89" t="str">
-        <v>EA</v>
+        <v>Set</v>
       </c>
       <c r="J89">
-        <v>12000</v>
+        <v>300</v>
       </c>
       <c r="K89">
         <v>0</v>
       </c>
       <c r="L89">
-        <v>12000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>TAX-2608-001</v>
+        <v>QT-2609-001</v>
       </c>
       <c r="B90" t="str">
-        <v>TAX_INVOICE</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C90" t="str">
-        <v>2026-08-20</v>
+        <v>2026-09-24</v>
       </c>
       <c r="D90" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E90">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F90" t="str">
-        <v>PLC-DC-001</v>
+        <v>OR-PCB-01</v>
       </c>
       <c r="G90" t="str">
-        <v>4. PLC Data Center Line 1 SET</v>
+        <v>PC Board</v>
       </c>
       <c r="H90">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I90" t="str">
-        <v>SET</v>
+        <v>EA</v>
       </c>
       <c r="J90">
-        <v>150000</v>
+        <v>13000</v>
       </c>
       <c r="K90">
         <v>0</v>
       </c>
       <c r="L90">
-        <v>150000</v>
+        <v>260000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>TAX-2608-001</v>
+        <v>QT-2609-001</v>
       </c>
       <c r="B91" t="str">
-        <v>TAX_INVOICE</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C91" t="str">
-        <v>2026-08-20</v>
+        <v>2026-09-24</v>
       </c>
       <c r="D91" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E91">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F91" t="str">
-        <v>STR-SUP-001</v>
+        <v>OR-DIO-01</v>
       </c>
       <c r="G91" t="str">
-        <v>5. Structure Support</v>
+        <v>Board Digital Input / Output</v>
       </c>
       <c r="H91">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I91" t="str">
-        <v>SET</v>
+        <v>EA</v>
       </c>
       <c r="J91">
-        <v>20000</v>
+        <v>5500</v>
       </c>
       <c r="K91">
         <v>0</v>
       </c>
       <c r="L91">
-        <v>20000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>TAX-2608-001</v>
+        <v>QT-2609-001</v>
       </c>
       <c r="B92" t="str">
-        <v>TAX_INVOICE</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C92" t="str">
-        <v>2026-08-20</v>
+        <v>2026-09-24</v>
       </c>
       <c r="D92" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E92">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F92" t="str">
-        <v>PC-CTR-001</v>
+        <v>OR-PSU-01</v>
       </c>
       <c r="G92" t="str">
-        <v>6. PC Center</v>
+        <v>AC To DC Power</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I92" t="str">
-        <v>SET</v>
+        <v>EA</v>
       </c>
       <c r="J92">
-        <v>123000</v>
+        <v>2950</v>
       </c>
       <c r="K92">
         <v>0</v>
       </c>
       <c r="L92">
-        <v>123000</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>PO-2609-001</v>
+        <v>QT-2609-001</v>
       </c>
       <c r="B93" t="str">
-        <v>PURCHASE_ORDER</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C93" t="str">
         <v>2026-09-24</v>
       </c>
       <c r="D93" t="str">
-        <v>บริษัท ออมรอน อีเลคทรอนิกส์ (ประเทศไทย) จำกัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E93">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F93" t="str">
-        <v>SPINDLE-ROLL-01</v>
+        <v>OR-BOX-ACC-01</v>
       </c>
       <c r="G93" t="str">
-        <v>Roller Paper Printer Spindle (แกนหมุนกระดาษเครื่องพิมพ์อัปเกรด)</v>
+        <v>Box Control &amp; Accessories</v>
       </c>
       <c r="H93">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I93" t="str">
-        <v>Set</v>
+        <v>EA</v>
       </c>
       <c r="J93">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="K93">
         <v>0</v>
       </c>
       <c r="L93">
-        <v>4500</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>PO-2609-001</v>
+        <v>QT-2609-001</v>
       </c>
       <c r="B94" t="str">
-        <v>PURCHASE_ORDER</v>
+        <v>QUOTATION</v>
       </c>
       <c r="C94" t="str">
         <v>2026-09-24</v>
       </c>
       <c r="D94" t="str">
-        <v>บริษัท ออมรอน อีเลคทรอนิกส์ (ประเทศไทย) จำกัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E94">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F94" t="str">
-        <v>BOX-MINI-JB01</v>
+        <v>OR-SRV-01</v>
       </c>
       <c r="G94" t="str">
-        <v>mini junction box</v>
+        <v>ติดตั้ง &amp; ทดสอบระบบ (System Installation &amp; Testing) (2 คน x 4 วัน)</v>
       </c>
       <c r="H94">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I94" t="str">
-        <v>Set</v>
+        <v>วัน</v>
       </c>
       <c r="J94">
-        <v>300</v>
+        <v>10000</v>
       </c>
       <c r="K94">
         <v>0</v>
       </c>
       <c r="L94">
-        <v>4500</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>QT-2609-001</v>
+        <v>QT-2609-003</v>
       </c>
       <c r="B95" t="str">
         <v>QUOTATION</v>
@@ -8563,30 +8375,30 @@
         <v>1</v>
       </c>
       <c r="F95" t="str">
-        <v>OR-PCB-01</v>
+        <v>CONV-USB-LAN</v>
       </c>
       <c r="G95" t="str">
-        <v>PC Board</v>
+        <v>Convert USB to Lan</v>
       </c>
       <c r="H95">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I95" t="str">
-        <v>EA</v>
+        <v>Sets</v>
       </c>
       <c r="J95">
-        <v>13000</v>
+        <v>1500</v>
       </c>
       <c r="K95">
         <v>0</v>
       </c>
       <c r="L95">
-        <v>260000</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>QT-2609-001</v>
+        <v>QT-2609-003</v>
       </c>
       <c r="B96" t="str">
         <v>QUOTATION</v>
@@ -8601,30 +8413,30 @@
         <v>2</v>
       </c>
       <c r="F96" t="str">
-        <v>OR-DIO-01</v>
+        <v>PWR-DC-DC</v>
       </c>
       <c r="G96" t="str">
-        <v>Board Digital Input / Output</v>
+        <v>Power DC to DC Converter</v>
       </c>
       <c r="H96">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I96" t="str">
-        <v>EA</v>
+        <v>Sets</v>
       </c>
       <c r="J96">
-        <v>5500</v>
+        <v>1990</v>
       </c>
       <c r="K96">
         <v>0</v>
       </c>
       <c r="L96">
-        <v>110000</v>
+        <v>29850</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>QT-2609-001</v>
+        <v>QT-2609-003</v>
       </c>
       <c r="B97" t="str">
         <v>QUOTATION</v>
@@ -8639,30 +8451,30 @@
         <v>3</v>
       </c>
       <c r="F97" t="str">
-        <v>OR-PSU-01</v>
+        <v>SW-HUB-5P-1</v>
       </c>
       <c r="G97" t="str">
-        <v>AC To DC Power</v>
+        <v>Switching Hub 5 Port</v>
       </c>
       <c r="H97">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I97" t="str">
-        <v>EA</v>
+        <v>Sets</v>
       </c>
       <c r="J97">
-        <v>2950</v>
+        <v>1500</v>
       </c>
       <c r="K97">
         <v>0</v>
       </c>
       <c r="L97">
-        <v>59000</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>QT-2609-001</v>
+        <v>QT-2609-003</v>
       </c>
       <c r="B98" t="str">
         <v>QUOTATION</v>
@@ -8677,30 +8489,30 @@
         <v>4</v>
       </c>
       <c r="F98" t="str">
-        <v>OR-BOX-ACC-01</v>
+        <v>LAN-CAT6-100M</v>
       </c>
       <c r="G98" t="str">
-        <v>Box Control &amp; Accessories</v>
+        <v>สาย Lan Cat6 ความยาว 100 เมตร</v>
       </c>
       <c r="H98">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I98" t="str">
-        <v>EA</v>
+        <v>Sets</v>
       </c>
       <c r="J98">
-        <v>5000</v>
+        <v>3600</v>
       </c>
       <c r="K98">
         <v>0</v>
       </c>
       <c r="L98">
-        <v>100000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>QT-2609-001</v>
+        <v>QT-2609-003</v>
       </c>
       <c r="B99" t="str">
         <v>QUOTATION</v>
@@ -8715,30 +8527,30 @@
         <v>5</v>
       </c>
       <c r="F99" t="str">
-        <v>OR-SRV-01</v>
+        <v>SW-HUB-5P-IND</v>
       </c>
       <c r="G99" t="str">
-        <v>ติดตั้ง &amp; ทดสอบระบบ (System Installation &amp; Testing) (2 คน x 4 วัน)</v>
+        <v>Switching Hub 5 Port (Industrial)</v>
       </c>
       <c r="H99">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I99" t="str">
-        <v>วัน</v>
+        <v>Set</v>
       </c>
       <c r="J99">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="K99">
         <v>0</v>
       </c>
       <c r="L99">
-        <v>40000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>QT-2609-002</v>
+        <v>QT-2609-003</v>
       </c>
       <c r="B100" t="str">
         <v>QUOTATION</v>
@@ -8747,31 +8559,31 @@
         <v>2026-09-24</v>
       </c>
       <c r="D100" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E100">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F100" t="str">
-        <v>SYS-SMARTCAM-AI</v>
+        <v>ROLLER-PRN</v>
       </c>
       <c r="G100" t="str">
-        <v>ชุดระบบ Smart Camera Pick &amp; Place / MVC with Camera 12 MP Inspection Parts (Wenglor)</v>
+        <v>Roller Paper Printer</v>
       </c>
       <c r="H100">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I100" t="str">
-        <v>ชุด</v>
+        <v>Sets</v>
       </c>
       <c r="J100">
-        <v>1004354</v>
+        <v>1200</v>
       </c>
       <c r="K100">
         <v>0</v>
       </c>
       <c r="L100">
-        <v>1004354</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="101">
@@ -8788,458 +8600,230 @@
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="E101">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F101" t="str">
-        <v>CONV-USB-LAN</v>
+        <v>SRV-INSTALL-NET</v>
       </c>
       <c r="G101" t="str">
-        <v>Convert USB to Lan</v>
+        <v>ค่าบริการติดตั้ง</v>
       </c>
       <c r="H101">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I101" t="str">
-        <v>Sets</v>
+        <v>Job</v>
       </c>
       <c r="J101">
-        <v>1500</v>
+        <v>45000</v>
       </c>
       <c r="K101">
         <v>0</v>
       </c>
       <c r="L101">
-        <v>22500</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>QT-2609-003</v>
+        <v>QT-2609-004</v>
       </c>
       <c r="B102" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C102" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="D102" t="str">
-        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
       </c>
       <c r="E102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" t="str">
-        <v>PWR-DC-DC</v>
+        <v>COMP-DELL-5090</v>
       </c>
       <c r="G102" t="str">
-        <v>Power DC to DC Converter</v>
+        <v>ชุดคอมพิวเตอร์ Dell OptiPlex 5090 SFF (Dashboard Data Monitor Set)</v>
       </c>
       <c r="H102">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I102" t="str">
-        <v>Sets</v>
+        <v>ชุด</v>
       </c>
       <c r="J102">
-        <v>1990</v>
+        <v>35000</v>
       </c>
       <c r="K102">
         <v>0</v>
       </c>
       <c r="L102">
-        <v>29850</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>QT-2609-003</v>
+        <v>QT-2609-004</v>
       </c>
       <c r="B103" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C103" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="D103" t="str">
-        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
       </c>
       <c r="E103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F103" t="str">
-        <v>SW-HUB-5P-1</v>
+        <v>MON-LED-24FHD</v>
       </c>
       <c r="G103" t="str">
-        <v>Switching Hub 5 Port</v>
+        <v>จอแสดงผล Dashboard LED Monitor 24 นิ้ว (Full HD)</v>
       </c>
       <c r="H103">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I103" t="str">
-        <v>Sets</v>
+        <v>ชุด</v>
       </c>
       <c r="J103">
-        <v>1500</v>
+        <v>7800</v>
       </c>
       <c r="K103">
         <v>0</v>
       </c>
       <c r="L103">
-        <v>22500</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>QT-2609-003</v>
+        <v>QT-2609-004</v>
       </c>
       <c r="B104" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C104" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="D104" t="str">
-        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
       </c>
       <c r="E104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F104" t="str">
-        <v>LAN-CAT6-100M</v>
+        <v>ACC-KBM-WL</v>
       </c>
       <c r="G104" t="str">
-        <v>สาย Lan Cat6 ความยาว 100 เมตร</v>
+        <v>ชุดคีย์บอร์ดและเมาส์ไร้สาย (Wireless Keyboard &amp; Mouse)</v>
       </c>
       <c r="H104">
         <v>1</v>
       </c>
       <c r="I104" t="str">
-        <v>Sets</v>
+        <v>ชุด</v>
       </c>
       <c r="J104">
-        <v>3600</v>
+        <v>890</v>
       </c>
       <c r="K104">
         <v>0</v>
       </c>
       <c r="L104">
-        <v>3600</v>
+        <v>890</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>QT-2609-003</v>
+        <v>QT-2609-004</v>
       </c>
       <c r="B105" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C105" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="D105" t="str">
-        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
       </c>
       <c r="E105">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F105" t="str">
-        <v>SW-HUB-5P-IND</v>
+        <v>UPS-800VA-480W</v>
       </c>
       <c r="G105" t="str">
-        <v>Switching Hub 5 Port (Industrial)</v>
+        <v>เครื่องสำรองไฟอัตโนมัติ (UPS 800VA / 480W)</v>
       </c>
       <c r="H105">
         <v>1</v>
       </c>
       <c r="I105" t="str">
-        <v>Set</v>
+        <v>เครื่อง</v>
       </c>
       <c r="J105">
-        <v>7000</v>
+        <v>3500</v>
       </c>
       <c r="K105">
         <v>0</v>
       </c>
       <c r="L105">
-        <v>7000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>QT-2609-003</v>
+        <v>QT-2609-005</v>
       </c>
       <c r="B106" t="str">
         <v>QUOTATION</v>
       </c>
       <c r="C106" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="D106" t="str">
-        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
       </c>
       <c r="E106">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F106" t="str">
-        <v>ROLLER-PRN</v>
+        <v>SRV-DASHBOARD-SW</v>
       </c>
       <c r="G106" t="str">
-        <v>Roller Paper Printer</v>
+        <v>โปรแกรม ระบบ Dashboard Data Monitor</v>
       </c>
       <c r="H106">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I106" t="str">
-        <v>Sets</v>
+        <v>Job</v>
       </c>
       <c r="J106">
-        <v>1200</v>
+        <v>150000</v>
       </c>
       <c r="K106">
         <v>0</v>
       </c>
       <c r="L106">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>QT-2609-003</v>
-      </c>
-      <c r="B107" t="str">
-        <v>QUOTATION</v>
-      </c>
-      <c r="C107" t="str">
-        <v>2026-09-24</v>
-      </c>
-      <c r="D107" t="str">
-        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
-      </c>
-      <c r="E107">
-        <v>7</v>
-      </c>
-      <c r="F107" t="str">
-        <v>SRV-INSTALL-NET</v>
-      </c>
-      <c r="G107" t="str">
-        <v>ค่าบริการติดตั้ง</v>
-      </c>
-      <c r="H107">
-        <v>1</v>
-      </c>
-      <c r="I107" t="str">
-        <v>Job</v>
-      </c>
-      <c r="J107">
-        <v>45000</v>
-      </c>
-      <c r="K107">
-        <v>0</v>
-      </c>
-      <c r="L107">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>QT-2609-004</v>
-      </c>
-      <c r="B108" t="str">
-        <v>QUOTATION</v>
-      </c>
-      <c r="C108" t="str">
-        <v>2026-09-25</v>
-      </c>
-      <c r="D108" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
-      </c>
-      <c r="E108">
-        <v>1</v>
-      </c>
-      <c r="F108" t="str">
-        <v>COMP-DELL-5090</v>
-      </c>
-      <c r="G108" t="str">
-        <v>ชุดคอมพิวเตอร์ Dell OptiPlex 5090 SFF (Dashboard Data Monitor Set)</v>
-      </c>
-      <c r="H108">
-        <v>1</v>
-      </c>
-      <c r="I108" t="str">
-        <v>ชุด</v>
-      </c>
-      <c r="J108">
-        <v>35000</v>
-      </c>
-      <c r="K108">
-        <v>0</v>
-      </c>
-      <c r="L108">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>QT-2609-004</v>
-      </c>
-      <c r="B109" t="str">
-        <v>QUOTATION</v>
-      </c>
-      <c r="C109" t="str">
-        <v>2026-09-25</v>
-      </c>
-      <c r="D109" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
-      </c>
-      <c r="E109">
-        <v>2</v>
-      </c>
-      <c r="F109" t="str">
-        <v>MON-LED-24FHD</v>
-      </c>
-      <c r="G109" t="str">
-        <v>จอแสดงผล Dashboard LED Monitor 24 นิ้ว (Full HD)</v>
-      </c>
-      <c r="H109">
-        <v>1</v>
-      </c>
-      <c r="I109" t="str">
-        <v>ชุด</v>
-      </c>
-      <c r="J109">
-        <v>7800</v>
-      </c>
-      <c r="K109">
-        <v>0</v>
-      </c>
-      <c r="L109">
-        <v>7800</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>QT-2609-004</v>
-      </c>
-      <c r="B110" t="str">
-        <v>QUOTATION</v>
-      </c>
-      <c r="C110" t="str">
-        <v>2026-09-25</v>
-      </c>
-      <c r="D110" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
-      </c>
-      <c r="E110">
-        <v>3</v>
-      </c>
-      <c r="F110" t="str">
-        <v>ACC-KBM-WL</v>
-      </c>
-      <c r="G110" t="str">
-        <v>ชุดคีย์บอร์ดและเมาส์ไร้สาย (Wireless Keyboard &amp; Mouse)</v>
-      </c>
-      <c r="H110">
-        <v>1</v>
-      </c>
-      <c r="I110" t="str">
-        <v>ชุด</v>
-      </c>
-      <c r="J110">
-        <v>890</v>
-      </c>
-      <c r="K110">
-        <v>0</v>
-      </c>
-      <c r="L110">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>QT-2609-004</v>
-      </c>
-      <c r="B111" t="str">
-        <v>QUOTATION</v>
-      </c>
-      <c r="C111" t="str">
-        <v>2026-09-25</v>
-      </c>
-      <c r="D111" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
-      </c>
-      <c r="E111">
-        <v>4</v>
-      </c>
-      <c r="F111" t="str">
-        <v>UPS-800VA-480W</v>
-      </c>
-      <c r="G111" t="str">
-        <v>เครื่องสำรองไฟอัตโนมัติ (UPS 800VA / 480W)</v>
-      </c>
-      <c r="H111">
-        <v>1</v>
-      </c>
-      <c r="I111" t="str">
-        <v>เครื่อง</v>
-      </c>
-      <c r="J111">
-        <v>3500</v>
-      </c>
-      <c r="K111">
-        <v>0</v>
-      </c>
-      <c r="L111">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>QT-2609-005</v>
-      </c>
-      <c r="B112" t="str">
-        <v>QUOTATION</v>
-      </c>
-      <c r="C112" t="str">
-        <v>2026-09-25</v>
-      </c>
-      <c r="D112" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
-      </c>
-      <c r="E112">
-        <v>1</v>
-      </c>
-      <c r="F112" t="str">
-        <v>SRV-DASHBOARD-SW</v>
-      </c>
-      <c r="G112" t="str">
-        <v>โปรแกรม ระบบ Dashboard Data Monitor</v>
-      </c>
-      <c r="H112">
-        <v>1</v>
-      </c>
-      <c r="I112" t="str">
-        <v>Job</v>
-      </c>
-      <c r="J112">
-        <v>150000</v>
-      </c>
-      <c r="K112">
-        <v>0</v>
-      </c>
-      <c r="L112">
         <v>150000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L112"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L106"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9284,116 +8868,116 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>plan-pnp-solenoid</v>
+        <v>plan-pnp-po2607001</v>
       </c>
       <c r="B2" t="str">
-        <v>โครงการระบบตรวจสอบย้อนกลับ Solenoid Line (5 สถานี)</v>
+        <v>โครงการชุดบอร์ดควบคุม PLC Line ADC &amp; Data Center Line</v>
       </c>
       <c r="C2" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="D2" t="str">
-        <v>2505004</v>
+        <v>2607001</v>
       </c>
       <c r="E2" t="str">
-        <v>QT-2505-004</v>
+        <v>QT-2607-001</v>
       </c>
       <c r="F2">
-        <v>2323499.85</v>
+        <v>2610620.24</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="str">
-        <v>งวดที่ 1: เงินมัดจำลงนามสัญญาและสั่งซื้ออุปกรณ์หลัก (50%)</v>
+        <v>งวดที่ 1: มัดจำลงนามสัญญาและสั่งซื้ออุปกรณ์ PLC Control Board (50%)</v>
       </c>
       <c r="I2">
         <v>50</v>
       </c>
       <c r="J2">
-        <v>1161749.93</v>
+        <v>1305310.12</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-05-20</v>
+        <v>2026-07-30</v>
       </c>
       <c r="L2" t="str">
-        <v>PAID</v>
+        <v>INVOICED</v>
       </c>
       <c r="M2" t="str">
-        <v>INV-690800001</v>
+        <v>INV-2608-001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>plan-pnp-solenoid</v>
+        <v>plan-pnp-po2607001</v>
       </c>
       <c r="B3" t="str">
-        <v>โครงการระบบตรวจสอบย้อนกลับ Solenoid Line (5 สถานี)</v>
+        <v>โครงการชุดบอร์ดควบคุม PLC Line ADC &amp; Data Center Line</v>
       </c>
       <c r="C3" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="D3" t="str">
-        <v>2505004</v>
+        <v>2607001</v>
       </c>
       <c r="E3" t="str">
-        <v>QT-2505-004</v>
+        <v>QT-2607-001</v>
       </c>
       <c r="F3">
-        <v>2323499.85</v>
+        <v>2610620.24</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3" t="str">
-        <v>งวดที่ 2: ติดตั้งซอฟต์แวร์และทดสอบระบบ Factory Acceptance Test (40%)</v>
+        <v>งวดที่ 2: วายริ่งตู้ ติดตั้งระบบหน้างาน และทดสอบระบบ FAT (40%)</v>
       </c>
       <c r="I3">
         <v>40</v>
       </c>
       <c r="J3">
-        <v>929399.94</v>
+        <v>1044248.1</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-08-30</v>
+        <v>2026-09-15</v>
       </c>
       <c r="L3" t="str">
-        <v>INVOICED</v>
+        <v>WAITING</v>
       </c>
       <c r="M3" t="str">
-        <v>INV-690600005</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>plan-pnp-solenoid</v>
+        <v>plan-pnp-po2607001</v>
       </c>
       <c r="B4" t="str">
-        <v>โครงการระบบตรวจสอบย้อนกลับ Solenoid Line (5 สถานี)</v>
+        <v>โครงการชุดบอร์ดควบคุม PLC Line ADC &amp; Data Center Line</v>
       </c>
       <c r="C4" t="str">
         <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="D4" t="str">
-        <v>2505004</v>
+        <v>2607001</v>
       </c>
       <c r="E4" t="str">
-        <v>QT-2505-004</v>
+        <v>QT-2607-001</v>
       </c>
       <c r="F4">
-        <v>2323499.85</v>
+        <v>2610620.24</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4" t="str">
-        <v>งวดที่ 3: ส่งมอบงานขั้นสุดท้าย Site Acceptance Test &amp; Training (10%)</v>
+        <v>งวดที่ 3: ส่งมอบงานขั้นสุดท้าย SAT &amp; ตรวจรับระบบสมบูรณ์ (10%)</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4">
-        <v>232349.98</v>
+        <v>261062.02</v>
       </c>
       <c r="K4" t="str">
         <v>2026-10-31</v>
@@ -9407,119 +8991,119 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>plan-tsf-autopack</v>
+        <v>plan-pnp-po2605001</v>
       </c>
       <c r="B5" t="str">
-        <v>เครื่องจักร TSF1 Auto pack LM1 (Stacker &amp; Bag Insert)</v>
+        <v>โครงการระบบสายการผลิต Zone 1-6 (Fujipart Thailand)</v>
       </c>
       <c r="C5" t="str">
-        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="D5" t="str">
-        <v>TSF-PO-2601</v>
+        <v>2605001</v>
       </c>
       <c r="E5" t="str">
-        <v>QT-2601-TSF</v>
+        <v>QT-2605-001</v>
       </c>
       <c r="F5">
-        <v>2442800</v>
+        <v>2580305</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5" t="str">
-        <v>งวดที่ 1: เงินมัดจำเริ่มงานออกแบบและสั่งผลิตชิ้นส่วน (30%)</v>
+        <v>งวดที่ 1: เงินมัดจำเริ่มต้นโครงการและจัดซื้อชิ้นส่วนมาตรฐาน (30%)</v>
       </c>
       <c r="I5">
         <v>30</v>
       </c>
       <c r="J5">
-        <v>732840</v>
+        <v>774091.5</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-01-30</v>
+        <v>2026-05-20</v>
       </c>
       <c r="L5" t="str">
         <v>PAID</v>
       </c>
       <c r="M5" t="str">
-        <v>INV-2601-TSF1</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>plan-tsf-autopack</v>
+        <v>plan-pnp-po2605001</v>
       </c>
       <c r="B6" t="str">
-        <v>เครื่องจักร TSF1 Auto pack LM1 (Stacker &amp; Bag Insert)</v>
+        <v>โครงการระบบสายการผลิต Zone 1-6 (Fujipart Thailand)</v>
       </c>
       <c r="C6" t="str">
-        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="D6" t="str">
-        <v>TSF-PO-2601</v>
+        <v>2605001</v>
       </c>
       <c r="E6" t="str">
-        <v>QT-2601-TSF</v>
+        <v>QT-2605-001</v>
       </c>
       <c r="F6">
-        <v>2442800</v>
+        <v>2580305</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
       <c r="H6" t="str">
-        <v>งวดที่ 2: ประกอบเครื่องจักร ติดตั้งระบบไฟฟ้า &amp; FAT (50%)</v>
+        <v>งวดที่ 2: ประกอบชิ้นงานและติดตั้งระบบหน้างาน Zone 1-6 (50%)</v>
       </c>
       <c r="I6">
         <v>50</v>
       </c>
       <c r="J6">
-        <v>1221400</v>
+        <v>1290152.5</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-06-15</v>
+        <v>2026-08-30</v>
       </c>
       <c r="L6" t="str">
-        <v>INVOICED</v>
+        <v>WAITING</v>
       </c>
       <c r="M6" t="str">
-        <v>INV-2603-TSF2</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>plan-tsf-autopack</v>
+        <v>plan-pnp-po2605001</v>
       </c>
       <c r="B7" t="str">
-        <v>เครื่องจักร TSF1 Auto pack LM1 (Stacker &amp; Bag Insert)</v>
+        <v>โครงการระบบสายการผลิต Zone 1-6 (Fujipart Thailand)</v>
       </c>
       <c r="C7" t="str">
-        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="D7" t="str">
-        <v>TSF-PO-2601</v>
+        <v>2605001</v>
       </c>
       <c r="E7" t="str">
-        <v>QT-2601-TSF</v>
+        <v>QT-2605-001</v>
       </c>
       <c r="F7">
-        <v>2442800</v>
+        <v>2580305</v>
       </c>
       <c r="G7">
         <v>3</v>
       </c>
       <c r="H7" t="str">
-        <v>งวดที่ 3: ส่งมอบเครื่องจักรหน้างานและตรวจรับ SAT (20%)</v>
+        <v>งวดที่ 3: ส่งมอบงานและตรวจรับ SAT สมบูรณ์ (20%)</v>
       </c>
       <c r="I7">
         <v>20</v>
       </c>
       <c r="J7">
-        <v>488560</v>
+        <v>516061</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-11-15</v>
+        <v>2026-10-31</v>
       </c>
       <c r="L7" t="str">
         <v>WAITING</v>
@@ -9530,34 +9114,34 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>plan-kuroda-vision</v>
+        <v>plan-pnp-po2605002</v>
       </c>
       <c r="B8" t="str">
-        <v>ชุดระบบกล้องตรวจสอบชิ้นงาน AI Vision Machine B60</v>
+        <v>โครงการระบบสายการผลิต Zone 7 (Fujipart Thailand)</v>
       </c>
       <c r="C8" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="D8" t="str">
-        <v>KURODA-PO-089</v>
+        <v>2605002</v>
       </c>
       <c r="E8" t="str">
-        <v>QT-2605-KUR</v>
+        <v>QT-2605-002</v>
       </c>
       <c r="F8">
-        <v>1074658.78</v>
+        <v>1260246</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="str">
-        <v>งวดที่ 1: เงินมัดจำและสั่งซื้ออุปกรณ์ Vision Hardware (50%)</v>
+        <v>งวดที่ 1: เงินมัดจำเริ่มต้นโครงการ 30% (Downpayment 30%)</v>
       </c>
       <c r="I8">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J8">
-        <v>537329.39</v>
+        <v>378073.8</v>
       </c>
       <c r="K8" t="str">
         <v>2026-05-25</v>
@@ -9566,42 +9150,42 @@
         <v>PAID</v>
       </c>
       <c r="M8" t="str">
-        <v>INV-2605-001</v>
+        <v>REC-2605-002/1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>plan-kuroda-vision</v>
+        <v>plan-pnp-po2605002</v>
       </c>
       <c r="B9" t="str">
-        <v>ชุดระบบกล้องตรวจสอบชิ้นงาน AI Vision Machine B60</v>
+        <v>โครงการระบบสายการผลิต Zone 7 (Fujipart Thailand)</v>
       </c>
       <c r="C9" t="str">
-        <v>บริษัท คูโรดา เทคโน ทูลลิง แมชชีน (ไทยแลนด์) จํากัด</v>
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
       </c>
       <c r="D9" t="str">
-        <v>KURODA-PO-089</v>
+        <v>2605002</v>
       </c>
       <c r="E9" t="str">
-        <v>QT-2605-KUR</v>
+        <v>QT-2605-002</v>
       </c>
       <c r="F9">
-        <v>1074658.78</v>
+        <v>1260246</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="str">
-        <v>งวดที่ 2: ติดตั้งหน้างาน สอบเทียบความแม่นยำ AI &amp; ส่งมอบ (50%)</v>
+        <v>งวดที่ 2: ประกอบชิ้นงานและติดตั้งระบบหน้างาน Zone 7 (50%)</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9">
-        <v>537329.39</v>
+        <v>630123</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-10-15</v>
+        <v>2026-08-30</v>
       </c>
       <c r="L9" t="str">
         <v>WAITING</v>
@@ -9610,9 +9194,460 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>plan-pnp-po2605002</v>
+      </c>
+      <c r="B10" t="str">
+        <v>โครงการระบบสายการผลิต Zone 7 (Fujipart Thailand)</v>
+      </c>
+      <c r="C10" t="str">
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2605002</v>
+      </c>
+      <c r="E10" t="str">
+        <v>QT-2605-002</v>
+      </c>
+      <c r="F10">
+        <v>1260246</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10" t="str">
+        <v>งวดที่ 3: ส่งมอบงานและตรวจรับ SAT สมบูรณ์ (20%)</v>
+      </c>
+      <c r="I10">
+        <v>20</v>
+      </c>
+      <c r="J10">
+        <v>252049.2</v>
+      </c>
+      <c r="K10" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="L10" t="str">
+        <v>WAITING</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>plan-pnp-po2505005</v>
+      </c>
+      <c r="B11" t="str">
+        <v>โครงการซอฟต์แวร์ Traceability Solenoid Line Software &amp; Expansion</v>
+      </c>
+      <c r="C11" t="str">
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2505005</v>
+      </c>
+      <c r="E11" t="str">
+        <v>QT-2505-005</v>
+      </c>
+      <c r="F11">
+        <v>2325558.33</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="str">
+        <v>งวดที่ 1: เงินมัดจำลงนามและเริ่มพัฒนาซอฟต์แวร์ 30% (Downpayment 30%)</v>
+      </c>
+      <c r="I11">
+        <v>30</v>
+      </c>
+      <c r="J11">
+        <v>697667.5</v>
+      </c>
+      <c r="K11" t="str">
+        <v>2025-06-10</v>
+      </c>
+      <c r="L11" t="str">
+        <v>PAID</v>
+      </c>
+      <c r="M11" t="str">
+        <v>REC-2505-005/1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>plan-pnp-po2505005</v>
+      </c>
+      <c r="B12" t="str">
+        <v>โครงการซอฟต์แวร์ Traceability Solenoid Line Software &amp; Expansion</v>
+      </c>
+      <c r="C12" t="str">
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2505005</v>
+      </c>
+      <c r="E12" t="str">
+        <v>QT-2505-005</v>
+      </c>
+      <c r="F12">
+        <v>2325558.33</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12" t="str">
+        <v>งวดที่ 2: ติดตั้งซอฟต์แวร์และทดสอบ Test Run &amp; BuyOff (60%)</v>
+      </c>
+      <c r="I12">
+        <v>60</v>
+      </c>
+      <c r="J12">
+        <v>1395335</v>
+      </c>
+      <c r="K12" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="L12" t="str">
+        <v>PAID</v>
+      </c>
+      <c r="M12" t="str">
+        <v>REC-2505-005/2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>plan-pnp-po2505005</v>
+      </c>
+      <c r="B13" t="str">
+        <v>โครงการซอฟต์แวร์ Traceability Solenoid Line Software &amp; Expansion</v>
+      </c>
+      <c r="C13" t="str">
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2505005</v>
+      </c>
+      <c r="E13" t="str">
+        <v>QT-2505-005</v>
+      </c>
+      <c r="F13">
+        <v>2325558.33</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13" t="str">
+        <v>งวดที่ 3: ส่งมอบคู่มือการใช้งานและฝึกอบรม Manual &amp; Training (10%)</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <v>232555.83</v>
+      </c>
+      <c r="K13" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="L13" t="str">
+        <v>PAID</v>
+      </c>
+      <c r="M13" t="str">
+        <v>INV-690600005</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>plan-pnp-po2609002</v>
+      </c>
+      <c r="B14" t="str">
+        <v>โครงการจัดซื้ออุปกรณ์ Network &amp; งานบริการติดตั้ง</v>
+      </c>
+      <c r="C14" t="str">
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2609002</v>
+      </c>
+      <c r="E14" t="str">
+        <v>QT-2609-003</v>
+      </c>
+      <c r="F14">
+        <v>158841.5</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="str">
+        <v>งวดที่ 1: ส่งมอบอุปกรณ์ Network และบริการติดตั้งครบ 100%</v>
+      </c>
+      <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14">
+        <v>158841.5</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="L14" t="str">
+        <v>WAITING</v>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>plan-pnp-solenoid</v>
+      </c>
+      <c r="B15" t="str">
+        <v>โครงการซอฟต์แวร์ Traceability Solenoid Line IMV &amp; 5 Stations</v>
+      </c>
+      <c r="C15" t="str">
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2505004</v>
+      </c>
+      <c r="E15" t="str">
+        <v>QT-2505-004</v>
+      </c>
+      <c r="F15">
+        <v>4646999.71</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="str">
+        <v>งวดที่ 1: เงินมัดจำลงนามสัญญาและเริ่มดำเนินงาน (30%)</v>
+      </c>
+      <c r="I15">
+        <v>30</v>
+      </c>
+      <c r="J15">
+        <v>1394099.91</v>
+      </c>
+      <c r="K15" t="str">
+        <v>2025-05-20</v>
+      </c>
+      <c r="L15" t="str">
+        <v>PAID</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>plan-pnp-solenoid</v>
+      </c>
+      <c r="B16" t="str">
+        <v>โครงการซอฟต์แวร์ Traceability Solenoid Line IMV &amp; 5 Stations</v>
+      </c>
+      <c r="C16" t="str">
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2505004</v>
+      </c>
+      <c r="E16" t="str">
+        <v>QT-2505-004</v>
+      </c>
+      <c r="F16">
+        <v>4646999.71</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16" t="str">
+        <v>งวดที่ 2: ติดตั้งซอฟต์แวร์และทดสอบระบบ Factory Acceptance Test (50%)</v>
+      </c>
+      <c r="I16">
+        <v>50</v>
+      </c>
+      <c r="J16">
+        <v>2323499.86</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="L16" t="str">
+        <v>INVOICED</v>
+      </c>
+      <c r="M16" t="str">
+        <v>INV-690800001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>plan-pnp-solenoid</v>
+      </c>
+      <c r="B17" t="str">
+        <v>โครงการซอฟต์แวร์ Traceability Solenoid Line IMV &amp; 5 Stations</v>
+      </c>
+      <c r="C17" t="str">
+        <v>บริษัท พีเอ็นพี เทคโนโลยี เกรท จำกัด</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2505004</v>
+      </c>
+      <c r="E17" t="str">
+        <v>QT-2505-004</v>
+      </c>
+      <c r="F17">
+        <v>4646999.71</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17" t="str">
+        <v>งวดที่ 3: ส่งมอบงานขั้นสุดท้าย Site Acceptance Test &amp; Training (20%)</v>
+      </c>
+      <c r="I17">
+        <v>20</v>
+      </c>
+      <c r="J17">
+        <v>929399.94</v>
+      </c>
+      <c r="K17" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="L17" t="str">
+        <v>WAITING</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>plan-tsf-autopack</v>
+      </c>
+      <c r="B18" t="str">
+        <v>โครงการเครื่องจักร TSF1 Auto pack LM1 (Thai Sekisui Foam)</v>
+      </c>
+      <c r="C18" t="str">
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
+      </c>
+      <c r="D18" t="str">
+        <v>PO252155</v>
+      </c>
+      <c r="E18" t="str">
+        <v>QT-2512-2155</v>
+      </c>
+      <c r="F18">
+        <v>3793792</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="str">
+        <v>งวดที่ 1: เงินมัดจำลงนามสัญญาและสั่งซื้ออุปกรณ์หลัก (40% Downpayment)</v>
+      </c>
+      <c r="I18">
+        <v>40</v>
+      </c>
+      <c r="J18">
+        <v>1517516.8</v>
+      </c>
+      <c r="K18" t="str">
+        <v>2026-01-14</v>
+      </c>
+      <c r="L18" t="str">
+        <v>PAID</v>
+      </c>
+      <c r="M18" t="str">
+        <v>IV-690100001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>plan-tsf-autopack</v>
+      </c>
+      <c r="B19" t="str">
+        <v>โครงการเครื่องจักร TSF1 Auto pack LM1 (Thai Sekisui Foam)</v>
+      </c>
+      <c r="C19" t="str">
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
+      </c>
+      <c r="D19" t="str">
+        <v>PO252155</v>
+      </c>
+      <c r="E19" t="str">
+        <v>QT-2512-2155</v>
+      </c>
+      <c r="F19">
+        <v>3793792</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19" t="str">
+        <v>งวดที่ 2: ประกอบชิ้นส่วน ติดตั้งระบบไฟฟ้า &amp; FAT (30% After Process Work)</v>
+      </c>
+      <c r="I19">
+        <v>30</v>
+      </c>
+      <c r="J19">
+        <v>1138137.6</v>
+      </c>
+      <c r="K19" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="L19" t="str">
+        <v>WAITING</v>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>plan-tsf-autopack</v>
+      </c>
+      <c r="B20" t="str">
+        <v>โครงการเครื่องจักร TSF1 Auto pack LM1 (Thai Sekisui Foam)</v>
+      </c>
+      <c r="C20" t="str">
+        <v>บริษัท ไทย เซกิซุย โฟม จำกัด</v>
+      </c>
+      <c r="D20" t="str">
+        <v>PO252155</v>
+      </c>
+      <c r="E20" t="str">
+        <v>QT-2512-2155</v>
+      </c>
+      <c r="F20">
+        <v>3793792</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20" t="str">
+        <v>งวดที่ 3: ส่งมอบเครื่องจักรหน้างานและตรวจรับ SAT (30% After Complete Work)</v>
+      </c>
+      <c r="I20">
+        <v>30</v>
+      </c>
+      <c r="J20">
+        <v>1138137.6</v>
+      </c>
+      <c r="K20" t="str">
+        <v>2026-11-15</v>
+      </c>
+      <c r="L20" t="str">
+        <v>WAITING</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9726,7 +9761,7 @@
         <v>DO-2609-001</v>
       </c>
       <c r="J3" t="str">
-        <v>PRJ-KUR-B60</v>
+        <v>Vision Inspection Project</v>
       </c>
       <c r="K3" t="str">
         <v>ธนกฤต วิศวกรรม</v>
